--- a/DOC/DEG2000.xlsx
+++ b/DOC/DEG2000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\devel\1 DEG2000\DOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCEFADC-CFAA-4035-B4C9-C159D45E48F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DEFFCE-0A45-4290-AE93-F5B40BCD906A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22110" yWindow="5325" windowWidth="30900" windowHeight="25815" activeTab="1" xr2:uid="{F91C61BF-F393-4C13-9000-551DF6FEF055}"/>
+    <workbookView xWindow="3735" yWindow="2970" windowWidth="49620" windowHeight="27135" activeTab="14" xr2:uid="{F91C61BF-F393-4C13-9000-551DF6FEF055}"/>
   </bookViews>
   <sheets>
     <sheet name="DataGridView" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="1534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2832" uniqueCount="1534">
   <si>
     <t>cpuStatus</t>
   </si>
@@ -11299,119 +11299,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="316" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="317" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="320" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="321" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="322" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="81" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -11465,40 +11434,140 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="81" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="316" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="317" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="320" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="220" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="332" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="331" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="332" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="329" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="321" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="328" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="322" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="186" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="187" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="329" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="328" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="329" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="328" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="183" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11506,108 +11575,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="186" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="187" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="187" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="329" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="199" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="328" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="177" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="329" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="328" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="220" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="332" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="331" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="332" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="329" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="200" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="328" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="179" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="180" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="202" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="178" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="175" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="179" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="180" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="199" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="177" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="178" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="177" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="200" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="202" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="215" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15637,7 +15637,7 @@
       <c r="P6" s="1102"/>
       <c r="Q6" s="1102"/>
       <c r="R6" s="1102"/>
-      <c r="S6" s="997"/>
+      <c r="S6" s="1042"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
@@ -15658,7 +15658,7 @@
       <c r="P7" s="1104"/>
       <c r="Q7" s="1104"/>
       <c r="R7" s="1104"/>
-      <c r="S7" s="999"/>
+      <c r="S7" s="1044"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
@@ -15831,7 +15831,7 @@
       <c r="P15" s="1102"/>
       <c r="Q15" s="1102"/>
       <c r="R15" s="1102"/>
-      <c r="S15" s="997"/>
+      <c r="S15" s="1042"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
@@ -15852,7 +15852,7 @@
       <c r="P16" s="1104"/>
       <c r="Q16" s="1104"/>
       <c r="R16" s="1104"/>
-      <c r="S16" s="999"/>
+      <c r="S16" s="1044"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
@@ -15971,7 +15971,7 @@
       <c r="P24" s="1115"/>
       <c r="Q24" s="1115"/>
       <c r="R24" s="1115"/>
-      <c r="S24" s="1018"/>
+      <c r="S24" s="1009"/>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C25" s="173" t="s">
@@ -16021,7 +16021,7 @@
       <c r="P26" s="1102"/>
       <c r="Q26" s="1102"/>
       <c r="R26" s="1102"/>
-      <c r="S26" s="997"/>
+      <c r="S26" s="1042"/>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
@@ -16042,7 +16042,7 @@
       <c r="P27" s="1104"/>
       <c r="Q27" s="1104"/>
       <c r="R27" s="1104"/>
-      <c r="S27" s="999"/>
+      <c r="S27" s="1044"/>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.25">
       <c r="K29" t="s">
@@ -18571,7 +18571,9 @@
       <c r="G21" s="875"/>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
-      <c r="J21" s="214"/>
+      <c r="J21" s="214" t="s">
+        <v>561</v>
+      </c>
       <c r="K21" s="215"/>
     </row>
     <row r="22" spans="4:11" x14ac:dyDescent="0.25">
@@ -19830,42 +19832,42 @@
       <c r="L3" s="115" t="s">
         <v>112</v>
       </c>
-      <c r="M3" s="996">
+      <c r="M3" s="995">
         <v>0</v>
       </c>
-      <c r="N3" s="1018"/>
-      <c r="O3" s="996" t="s">
+      <c r="N3" s="1009"/>
+      <c r="O3" s="995" t="s">
         <v>119</v>
       </c>
-      <c r="P3" s="1006"/>
-      <c r="Q3" s="1006"/>
-      <c r="R3" s="1006"/>
-      <c r="S3" s="1006"/>
-      <c r="T3" s="1007"/>
-      <c r="U3" s="979">
+      <c r="P3" s="996"/>
+      <c r="Q3" s="996"/>
+      <c r="R3" s="996"/>
+      <c r="S3" s="996"/>
+      <c r="T3" s="997"/>
+      <c r="U3" s="1007">
         <v>2</v>
       </c>
-      <c r="V3" s="979">
+      <c r="V3" s="1007">
         <v>3</v>
       </c>
-      <c r="W3" s="996">
+      <c r="W3" s="995">
         <v>4</v>
       </c>
-      <c r="X3" s="997"/>
-      <c r="Y3" s="979">
+      <c r="X3" s="1042"/>
+      <c r="Y3" s="1007">
         <v>5</v>
       </c>
-      <c r="AC3" s="1047" t="s">
+      <c r="AC3" s="986" t="s">
         <v>1438</v>
       </c>
-      <c r="AD3" s="1047"/>
-      <c r="AE3" s="1047"/>
-      <c r="AF3" s="1047"/>
-      <c r="AG3" s="1047"/>
-      <c r="AH3" s="1047"/>
-      <c r="AI3" s="1047"/>
-      <c r="AJ3" s="1047"/>
-      <c r="AK3" s="1047"/>
+      <c r="AD3" s="986"/>
+      <c r="AE3" s="986"/>
+      <c r="AF3" s="986"/>
+      <c r="AG3" s="986"/>
+      <c r="AH3" s="986"/>
+      <c r="AI3" s="986"/>
+      <c r="AJ3" s="986"/>
+      <c r="AK3" s="986"/>
     </row>
     <row r="4" spans="12:37" x14ac:dyDescent="0.25">
       <c r="L4" s="114" t="s">
@@ -19891,40 +19893,40 @@
       <c r="T4" s="142" t="s">
         <v>88</v>
       </c>
-      <c r="U4" s="1017"/>
-      <c r="V4" s="1017"/>
-      <c r="W4" s="998" t="s">
+      <c r="U4" s="1008"/>
+      <c r="V4" s="1008"/>
+      <c r="W4" s="1043" t="s">
         <v>320</v>
       </c>
-      <c r="X4" s="999"/>
-      <c r="Y4" s="980"/>
+      <c r="X4" s="1044"/>
+      <c r="Y4" s="1026"/>
       <c r="AB4" s="898"/>
-      <c r="AC4" s="1040" t="s">
+      <c r="AC4" s="979" t="s">
         <v>1389</v>
       </c>
-      <c r="AD4" s="1041"/>
-      <c r="AE4" s="1042" t="s">
+      <c r="AD4" s="980"/>
+      <c r="AE4" s="981" t="s">
         <v>1388</v>
       </c>
-      <c r="AF4" s="1043"/>
-      <c r="AG4" s="1040" t="s">
+      <c r="AF4" s="982"/>
+      <c r="AG4" s="979" t="s">
         <v>1390</v>
       </c>
-      <c r="AH4" s="1043"/>
-      <c r="AI4" s="1044" t="s">
+      <c r="AH4" s="982"/>
+      <c r="AI4" s="983" t="s">
         <v>1437</v>
       </c>
-      <c r="AJ4" s="1045"/>
-      <c r="AK4" s="1046"/>
+      <c r="AJ4" s="984"/>
+      <c r="AK4" s="985"/>
     </row>
     <row r="5" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L5" s="1035" t="s">
+      <c r="L5" s="987" t="s">
         <v>111</v>
       </c>
-      <c r="M5" s="1003" t="s">
+      <c r="M5" s="992" t="s">
         <v>113</v>
       </c>
-      <c r="N5" s="1019" t="s">
+      <c r="N5" s="1010" t="s">
         <v>324</v>
       </c>
       <c r="O5" s="61"/>
@@ -19937,19 +19939,19 @@
       <c r="T5" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="U5" s="1011" t="s">
+      <c r="U5" s="1001" t="s">
         <v>470</v>
       </c>
-      <c r="V5" s="1014" t="s">
+      <c r="V5" s="1004" t="s">
         <v>323</v>
       </c>
-      <c r="W5" s="990" t="s">
+      <c r="W5" s="1036" t="s">
         <v>311</v>
       </c>
-      <c r="X5" s="994" t="s">
+      <c r="X5" s="1040" t="s">
         <v>312</v>
       </c>
-      <c r="Y5" s="981" t="s">
+      <c r="Y5" s="1027" t="s">
         <v>114</v>
       </c>
       <c r="AB5" s="911">
@@ -19982,9 +19984,9 @@
       <c r="AK5" s="902"/>
     </row>
     <row r="6" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L6" s="1036"/>
-      <c r="M6" s="1004"/>
-      <c r="N6" s="1020"/>
+      <c r="L6" s="988"/>
+      <c r="M6" s="993"/>
+      <c r="N6" s="1011"/>
       <c r="O6" s="64"/>
       <c r="P6" s="65"/>
       <c r="Q6" s="65"/>
@@ -19993,11 +19995,11 @@
       <c r="T6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U6" s="1012"/>
-      <c r="V6" s="1015"/>
-      <c r="W6" s="991"/>
-      <c r="X6" s="995"/>
-      <c r="Y6" s="982"/>
+      <c r="U6" s="1002"/>
+      <c r="V6" s="1005"/>
+      <c r="W6" s="1037"/>
+      <c r="X6" s="1041"/>
+      <c r="Y6" s="1028"/>
       <c r="AB6" s="279">
         <v>2</v>
       </c>
@@ -20028,9 +20030,9 @@
       <c r="AK6" s="215"/>
     </row>
     <row r="7" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L7" s="1036"/>
-      <c r="M7" s="1004"/>
-      <c r="N7" s="1021"/>
+      <c r="L7" s="988"/>
+      <c r="M7" s="993"/>
+      <c r="N7" s="1012"/>
       <c r="O7" s="64"/>
       <c r="P7" s="65"/>
       <c r="Q7" s="65"/>
@@ -20039,13 +20041,13 @@
       <c r="T7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U7" s="1012"/>
-      <c r="V7" s="1015"/>
-      <c r="W7" s="992"/>
-      <c r="X7" s="1000" t="s">
+      <c r="U7" s="1002"/>
+      <c r="V7" s="1005"/>
+      <c r="W7" s="1038"/>
+      <c r="X7" s="1045" t="s">
         <v>317</v>
       </c>
-      <c r="Y7" s="982"/>
+      <c r="Y7" s="1028"/>
       <c r="AB7" s="279">
         <v>3</v>
       </c>
@@ -20076,9 +20078,9 @@
       <c r="AK7" s="215"/>
     </row>
     <row r="8" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L8" s="1037"/>
-      <c r="M8" s="1004"/>
-      <c r="N8" s="1024" t="s">
+      <c r="L8" s="989"/>
+      <c r="M8" s="993"/>
+      <c r="N8" s="1015" t="s">
         <v>309</v>
       </c>
       <c r="O8" s="108"/>
@@ -20091,11 +20093,11 @@
       <c r="T8" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U8" s="1012"/>
-      <c r="V8" s="1015"/>
-      <c r="W8" s="992"/>
-      <c r="X8" s="1001"/>
-      <c r="Y8" s="982"/>
+      <c r="U8" s="1002"/>
+      <c r="V8" s="1005"/>
+      <c r="W8" s="1038"/>
+      <c r="X8" s="1046"/>
+      <c r="Y8" s="1028"/>
       <c r="AB8" s="279">
         <v>4</v>
       </c>
@@ -20126,11 +20128,11 @@
       <c r="AK8" s="215"/>
     </row>
     <row r="9" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L9" s="1035" t="s">
+      <c r="L9" s="987" t="s">
         <v>110</v>
       </c>
-      <c r="M9" s="1004"/>
-      <c r="N9" s="1025"/>
+      <c r="M9" s="993"/>
+      <c r="N9" s="1016"/>
       <c r="O9" s="61"/>
       <c r="P9" s="62"/>
       <c r="Q9" s="62"/>
@@ -20141,13 +20143,13 @@
       <c r="T9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U9" s="1012"/>
-      <c r="V9" s="1015"/>
-      <c r="W9" s="992"/>
-      <c r="X9" s="995" t="s">
+      <c r="U9" s="1002"/>
+      <c r="V9" s="1005"/>
+      <c r="W9" s="1038"/>
+      <c r="X9" s="1041" t="s">
         <v>316</v>
       </c>
-      <c r="Y9" s="982"/>
+      <c r="Y9" s="1028"/>
       <c r="AB9" s="279">
         <v>5</v>
       </c>
@@ -20180,9 +20182,9 @@
       </c>
     </row>
     <row r="10" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L10" s="1036"/>
-      <c r="M10" s="1004"/>
-      <c r="N10" s="1025"/>
+      <c r="L10" s="988"/>
+      <c r="M10" s="993"/>
+      <c r="N10" s="1016"/>
       <c r="O10" s="64"/>
       <c r="P10" s="65"/>
       <c r="Q10" s="65"/>
@@ -20191,11 +20193,11 @@
       <c r="T10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U10" s="1012"/>
-      <c r="V10" s="1015"/>
-      <c r="W10" s="992"/>
-      <c r="X10" s="1002"/>
-      <c r="Y10" s="982"/>
+      <c r="U10" s="1002"/>
+      <c r="V10" s="1005"/>
+      <c r="W10" s="1038"/>
+      <c r="X10" s="1047"/>
+      <c r="Y10" s="1028"/>
       <c r="AB10" s="279">
         <v>6</v>
       </c>
@@ -20226,9 +20228,9 @@
       <c r="AK10" s="917"/>
     </row>
     <row r="11" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L11" s="1036"/>
-      <c r="M11" s="1004"/>
-      <c r="N11" s="1026"/>
+      <c r="L11" s="988"/>
+      <c r="M11" s="993"/>
+      <c r="N11" s="1017"/>
       <c r="O11" s="64"/>
       <c r="P11" s="65"/>
       <c r="Q11" s="65"/>
@@ -20237,13 +20239,13 @@
       <c r="T11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U11" s="1012"/>
-      <c r="V11" s="1015"/>
-      <c r="W11" s="992"/>
-      <c r="X11" s="1000" t="s">
+      <c r="U11" s="1002"/>
+      <c r="V11" s="1005"/>
+      <c r="W11" s="1038"/>
+      <c r="X11" s="1045" t="s">
         <v>315</v>
       </c>
-      <c r="Y11" s="982"/>
+      <c r="Y11" s="1028"/>
       <c r="AB11" s="279">
         <v>7</v>
       </c>
@@ -20274,9 +20276,9 @@
       <c r="AK11" s="215"/>
     </row>
     <row r="12" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L12" s="1037"/>
-      <c r="M12" s="1004"/>
-      <c r="N12" s="1022" t="s">
+      <c r="L12" s="989"/>
+      <c r="M12" s="993"/>
+      <c r="N12" s="1013" t="s">
         <v>308</v>
       </c>
       <c r="O12" s="80"/>
@@ -20289,11 +20291,11 @@
       <c r="T12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U12" s="1012"/>
-      <c r="V12" s="1015"/>
-      <c r="W12" s="992"/>
-      <c r="X12" s="1001"/>
-      <c r="Y12" s="982"/>
+      <c r="U12" s="1002"/>
+      <c r="V12" s="1005"/>
+      <c r="W12" s="1038"/>
+      <c r="X12" s="1046"/>
+      <c r="Y12" s="1028"/>
       <c r="Z12" s="201"/>
       <c r="AB12" s="279">
         <v>8</v>
@@ -20325,11 +20327,11 @@
       <c r="AK12" s="215"/>
     </row>
     <row r="13" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L13" s="1035" t="s">
+      <c r="L13" s="987" t="s">
         <v>109</v>
       </c>
-      <c r="M13" s="1004"/>
-      <c r="N13" s="1023"/>
+      <c r="M13" s="993"/>
+      <c r="N13" s="1014"/>
       <c r="O13" s="106"/>
       <c r="P13" s="107"/>
       <c r="Q13" s="107"/>
@@ -20340,13 +20342,13 @@
       <c r="T13" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U13" s="1012"/>
-      <c r="V13" s="1015"/>
-      <c r="W13" s="992"/>
-      <c r="X13" s="995" t="s">
+      <c r="U13" s="1002"/>
+      <c r="V13" s="1005"/>
+      <c r="W13" s="1038"/>
+      <c r="X13" s="1041" t="s">
         <v>314</v>
       </c>
-      <c r="Y13" s="982"/>
+      <c r="Y13" s="1028"/>
       <c r="Z13" s="202"/>
       <c r="AB13" s="279">
         <v>9</v>
@@ -20378,8 +20380,8 @@
       <c r="AK13" s="215"/>
     </row>
     <row r="14" spans="12:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L14" s="1036"/>
-      <c r="M14" s="1004"/>
+      <c r="L14" s="988"/>
+      <c r="M14" s="993"/>
       <c r="N14" s="203"/>
       <c r="O14" s="64"/>
       <c r="P14" s="65"/>
@@ -20389,11 +20391,11 @@
       <c r="T14" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U14" s="1012"/>
-      <c r="V14" s="1015"/>
-      <c r="W14" s="992"/>
-      <c r="X14" s="1002"/>
-      <c r="Y14" s="982"/>
+      <c r="U14" s="1002"/>
+      <c r="V14" s="1005"/>
+      <c r="W14" s="1038"/>
+      <c r="X14" s="1047"/>
+      <c r="Y14" s="1028"/>
       <c r="Z14" s="202"/>
       <c r="AB14" s="279">
         <v>10</v>
@@ -20425,8 +20427,8 @@
       <c r="AK14" s="215"/>
     </row>
     <row r="15" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L15" s="1036"/>
-      <c r="M15" s="1004"/>
+      <c r="L15" s="988"/>
+      <c r="M15" s="993"/>
       <c r="N15" s="204"/>
       <c r="O15" s="64"/>
       <c r="P15" s="65"/>
@@ -20436,13 +20438,13 @@
       <c r="T15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U15" s="1012"/>
-      <c r="V15" s="1015"/>
-      <c r="W15" s="992"/>
-      <c r="X15" s="1000" t="s">
+      <c r="U15" s="1002"/>
+      <c r="V15" s="1005"/>
+      <c r="W15" s="1038"/>
+      <c r="X15" s="1045" t="s">
         <v>313</v>
       </c>
-      <c r="Y15" s="982"/>
+      <c r="Y15" s="1028"/>
       <c r="Z15" s="202"/>
       <c r="AB15" s="279">
         <v>11</v>
@@ -20474,8 +20476,8 @@
       <c r="AK15" s="215"/>
     </row>
     <row r="16" spans="12:37" x14ac:dyDescent="0.25">
-      <c r="L16" s="1037"/>
-      <c r="M16" s="1004"/>
+      <c r="L16" s="989"/>
+      <c r="M16" s="993"/>
       <c r="N16" s="204"/>
       <c r="O16" s="108"/>
       <c r="P16" s="109"/>
@@ -20487,11 +20489,11 @@
       <c r="T16" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U16" s="1012"/>
-      <c r="V16" s="1015"/>
-      <c r="W16" s="993"/>
-      <c r="X16" s="1001"/>
-      <c r="Y16" s="982"/>
+      <c r="U16" s="1002"/>
+      <c r="V16" s="1005"/>
+      <c r="W16" s="1039"/>
+      <c r="X16" s="1046"/>
+      <c r="Y16" s="1028"/>
       <c r="Z16" s="202"/>
       <c r="AB16" s="279">
         <v>12</v>
@@ -20523,10 +20525,10 @@
       <c r="AK16" s="215"/>
     </row>
     <row r="17" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L17" s="1035" t="s">
+      <c r="L17" s="987" t="s">
         <v>108</v>
       </c>
-      <c r="M17" s="1004"/>
+      <c r="M17" s="993"/>
       <c r="N17" s="204"/>
       <c r="O17" s="61"/>
       <c r="P17" s="62"/>
@@ -20538,13 +20540,13 @@
       <c r="T17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U17" s="1012"/>
-      <c r="V17" s="1015"/>
-      <c r="W17" s="984" t="s">
+      <c r="U17" s="1002"/>
+      <c r="V17" s="1005"/>
+      <c r="W17" s="1030" t="s">
         <v>318</v>
       </c>
-      <c r="X17" s="985"/>
-      <c r="Y17" s="982"/>
+      <c r="X17" s="1031"/>
+      <c r="Y17" s="1028"/>
       <c r="Z17" s="202"/>
       <c r="AB17" s="279">
         <v>13</v>
@@ -20576,8 +20578,8 @@
       <c r="AK17" s="215"/>
     </row>
     <row r="18" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L18" s="1036"/>
-      <c r="M18" s="1004"/>
+      <c r="L18" s="988"/>
+      <c r="M18" s="993"/>
       <c r="N18" s="204"/>
       <c r="O18" s="64"/>
       <c r="P18" s="65"/>
@@ -20587,11 +20589,11 @@
       <c r="T18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U18" s="1012"/>
-      <c r="V18" s="1015"/>
-      <c r="W18" s="986"/>
-      <c r="X18" s="987"/>
-      <c r="Y18" s="982"/>
+      <c r="U18" s="1002"/>
+      <c r="V18" s="1005"/>
+      <c r="W18" s="1032"/>
+      <c r="X18" s="1033"/>
+      <c r="Y18" s="1028"/>
       <c r="Z18" s="202"/>
       <c r="AB18" s="279">
         <v>14</v>
@@ -20623,8 +20625,8 @@
       <c r="AK18" s="215"/>
     </row>
     <row r="19" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L19" s="1036"/>
-      <c r="M19" s="1004"/>
+      <c r="L19" s="988"/>
+      <c r="M19" s="993"/>
       <c r="N19" s="204"/>
       <c r="O19" s="64"/>
       <c r="P19" s="65"/>
@@ -20634,11 +20636,11 @@
       <c r="T19" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U19" s="1012"/>
-      <c r="V19" s="1015"/>
-      <c r="W19" s="986"/>
-      <c r="X19" s="987"/>
-      <c r="Y19" s="982"/>
+      <c r="U19" s="1002"/>
+      <c r="V19" s="1005"/>
+      <c r="W19" s="1032"/>
+      <c r="X19" s="1033"/>
+      <c r="Y19" s="1028"/>
       <c r="Z19" s="202"/>
       <c r="AB19" s="279">
         <v>15</v>
@@ -20670,8 +20672,8 @@
       <c r="AK19" s="207"/>
     </row>
     <row r="20" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L20" s="1037"/>
-      <c r="M20" s="1004"/>
+      <c r="L20" s="989"/>
+      <c r="M20" s="993"/>
       <c r="N20" s="204"/>
       <c r="O20" s="80" t="s">
         <v>73</v>
@@ -20687,11 +20689,11 @@
       <c r="T20" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="U20" s="1012"/>
-      <c r="V20" s="1015"/>
-      <c r="W20" s="986"/>
-      <c r="X20" s="987"/>
-      <c r="Y20" s="982"/>
+      <c r="U20" s="1002"/>
+      <c r="V20" s="1005"/>
+      <c r="W20" s="1032"/>
+      <c r="X20" s="1033"/>
+      <c r="Y20" s="1028"/>
       <c r="Z20" s="202"/>
       <c r="AB20" s="279">
         <v>16</v>
@@ -20723,10 +20725,10 @@
       <c r="AK20" s="207"/>
     </row>
     <row r="21" spans="2:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L21" s="1035" t="s">
+      <c r="L21" s="987" t="s">
         <v>107</v>
       </c>
-      <c r="M21" s="1004"/>
+      <c r="M21" s="993"/>
       <c r="N21" s="204"/>
       <c r="O21" s="78"/>
       <c r="P21" s="79"/>
@@ -20738,11 +20740,11 @@
       <c r="T21" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="U21" s="1012"/>
-      <c r="V21" s="1015"/>
-      <c r="W21" s="986"/>
-      <c r="X21" s="987"/>
-      <c r="Y21" s="982"/>
+      <c r="U21" s="1002"/>
+      <c r="V21" s="1005"/>
+      <c r="W21" s="1032"/>
+      <c r="X21" s="1033"/>
+      <c r="Y21" s="1028"/>
       <c r="Z21" s="202"/>
       <c r="AB21" s="279">
         <v>17</v>
@@ -20798,8 +20800,8 @@
       <c r="I22" s="193">
         <v>7759</v>
       </c>
-      <c r="L22" s="1036"/>
-      <c r="M22" s="1004"/>
+      <c r="L22" s="988"/>
+      <c r="M22" s="993"/>
       <c r="N22" s="204"/>
       <c r="O22" s="64"/>
       <c r="P22" s="65"/>
@@ -20809,11 +20811,11 @@
       <c r="T22" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U22" s="1012"/>
-      <c r="V22" s="1015"/>
-      <c r="W22" s="986"/>
-      <c r="X22" s="987"/>
-      <c r="Y22" s="982"/>
+      <c r="U22" s="1002"/>
+      <c r="V22" s="1005"/>
+      <c r="W22" s="1032"/>
+      <c r="X22" s="1033"/>
+      <c r="Y22" s="1028"/>
       <c r="AB22" s="279">
         <v>18</v>
       </c>
@@ -20847,8 +20849,8 @@
       <c r="D23" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="L23" s="1036"/>
-      <c r="M23" s="1004"/>
+      <c r="L23" s="988"/>
+      <c r="M23" s="993"/>
       <c r="N23" s="204"/>
       <c r="O23" s="80"/>
       <c r="P23" s="81"/>
@@ -20858,11 +20860,11 @@
       <c r="T23" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U23" s="1012"/>
-      <c r="V23" s="1015"/>
-      <c r="W23" s="986"/>
-      <c r="X23" s="987"/>
-      <c r="Y23" s="982"/>
+      <c r="U23" s="1002"/>
+      <c r="V23" s="1005"/>
+      <c r="W23" s="1032"/>
+      <c r="X23" s="1033"/>
+      <c r="Y23" s="1028"/>
       <c r="AB23" s="279">
         <v>19</v>
       </c>
@@ -20916,8 +20918,8 @@
         <v>302</v>
       </c>
       <c r="J24" s="173"/>
-      <c r="L24" s="1037"/>
-      <c r="M24" s="1004"/>
+      <c r="L24" s="989"/>
+      <c r="M24" s="993"/>
       <c r="N24" s="204"/>
       <c r="O24" s="108"/>
       <c r="P24" s="109"/>
@@ -20929,11 +20931,11 @@
       <c r="T24" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U24" s="1012"/>
-      <c r="V24" s="1015"/>
-      <c r="W24" s="986"/>
-      <c r="X24" s="987"/>
-      <c r="Y24" s="982"/>
+      <c r="U24" s="1002"/>
+      <c r="V24" s="1005"/>
+      <c r="W24" s="1032"/>
+      <c r="X24" s="1033"/>
+      <c r="Y24" s="1028"/>
       <c r="AB24" s="279">
         <v>20</v>
       </c>
@@ -20987,10 +20989,10 @@
         <v>30</v>
       </c>
       <c r="J25" s="288"/>
-      <c r="L25" s="1035" t="s">
+      <c r="L25" s="987" t="s">
         <v>106</v>
       </c>
-      <c r="M25" s="1004"/>
+      <c r="M25" s="993"/>
       <c r="N25" s="204"/>
       <c r="O25" s="61"/>
       <c r="P25" s="62"/>
@@ -21002,11 +21004,11 @@
       <c r="T25" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U25" s="1012"/>
-      <c r="V25" s="1015"/>
-      <c r="W25" s="986"/>
-      <c r="X25" s="987"/>
-      <c r="Y25" s="982"/>
+      <c r="U25" s="1002"/>
+      <c r="V25" s="1005"/>
+      <c r="W25" s="1032"/>
+      <c r="X25" s="1033"/>
+      <c r="Y25" s="1028"/>
       <c r="AB25" s="912">
         <v>21</v>
       </c>
@@ -21025,9 +21027,9 @@
       <c r="AK25" s="210"/>
     </row>
     <row r="26" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L26" s="1036"/>
-      <c r="M26" s="1004"/>
-      <c r="N26" s="1032" t="s">
+      <c r="L26" s="988"/>
+      <c r="M26" s="993"/>
+      <c r="N26" s="1023" t="s">
         <v>327</v>
       </c>
       <c r="O26" s="64"/>
@@ -21038,17 +21040,17 @@
       <c r="T26" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U26" s="1012"/>
-      <c r="V26" s="1015"/>
-      <c r="W26" s="986"/>
-      <c r="X26" s="987"/>
-      <c r="Y26" s="982"/>
+      <c r="U26" s="1002"/>
+      <c r="V26" s="1005"/>
+      <c r="W26" s="1032"/>
+      <c r="X26" s="1033"/>
+      <c r="Y26" s="1028"/>
     </row>
     <row r="27" spans="2:37" x14ac:dyDescent="0.25">
       <c r="H27" s="173"/>
-      <c r="L27" s="1036"/>
-      <c r="M27" s="1004"/>
-      <c r="N27" s="1033"/>
+      <c r="L27" s="988"/>
+      <c r="M27" s="993"/>
+      <c r="N27" s="1024"/>
       <c r="O27" s="80"/>
       <c r="P27" s="81"/>
       <c r="Q27" s="81"/>
@@ -21057,17 +21059,17 @@
       <c r="T27" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U27" s="1012"/>
-      <c r="V27" s="1015"/>
-      <c r="W27" s="986"/>
-      <c r="X27" s="987"/>
-      <c r="Y27" s="982"/>
+      <c r="U27" s="1002"/>
+      <c r="V27" s="1005"/>
+      <c r="W27" s="1032"/>
+      <c r="X27" s="1033"/>
+      <c r="Y27" s="1028"/>
     </row>
     <row r="28" spans="2:37" x14ac:dyDescent="0.25">
       <c r="H28" s="173"/>
-      <c r="L28" s="1037"/>
-      <c r="M28" s="1004"/>
-      <c r="N28" s="1033"/>
+      <c r="L28" s="989"/>
+      <c r="M28" s="993"/>
+      <c r="N28" s="1024"/>
       <c r="O28" s="80"/>
       <c r="P28" s="81"/>
       <c r="Q28" s="82" t="s">
@@ -21078,18 +21080,18 @@
       <c r="T28" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U28" s="1012"/>
-      <c r="V28" s="1015"/>
-      <c r="W28" s="986"/>
-      <c r="X28" s="987"/>
-      <c r="Y28" s="982"/>
+      <c r="U28" s="1002"/>
+      <c r="V28" s="1005"/>
+      <c r="W28" s="1032"/>
+      <c r="X28" s="1033"/>
+      <c r="Y28" s="1028"/>
     </row>
     <row r="29" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L29" s="1035" t="s">
+      <c r="L29" s="987" t="s">
         <v>105</v>
       </c>
-      <c r="M29" s="1004"/>
-      <c r="N29" s="1033"/>
+      <c r="M29" s="993"/>
+      <c r="N29" s="1024"/>
       <c r="O29" s="106"/>
       <c r="P29" s="107"/>
       <c r="Q29" s="107"/>
@@ -21100,16 +21102,16 @@
       <c r="T29" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U29" s="1012"/>
-      <c r="V29" s="1015"/>
-      <c r="W29" s="986"/>
-      <c r="X29" s="987"/>
-      <c r="Y29" s="982"/>
+      <c r="U29" s="1002"/>
+      <c r="V29" s="1005"/>
+      <c r="W29" s="1032"/>
+      <c r="X29" s="1033"/>
+      <c r="Y29" s="1028"/>
     </row>
     <row r="30" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L30" s="1036"/>
-      <c r="M30" s="1004"/>
-      <c r="N30" s="1034"/>
+      <c r="L30" s="988"/>
+      <c r="M30" s="993"/>
+      <c r="N30" s="1025"/>
       <c r="O30" s="64"/>
       <c r="P30" s="65"/>
       <c r="Q30" s="65"/>
@@ -21118,16 +21120,16 @@
       <c r="T30" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U30" s="1012"/>
-      <c r="V30" s="1015"/>
-      <c r="W30" s="986"/>
-      <c r="X30" s="987"/>
-      <c r="Y30" s="982"/>
+      <c r="U30" s="1002"/>
+      <c r="V30" s="1005"/>
+      <c r="W30" s="1032"/>
+      <c r="X30" s="1033"/>
+      <c r="Y30" s="1028"/>
     </row>
     <row r="31" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L31" s="1036"/>
-      <c r="M31" s="1004"/>
-      <c r="N31" s="1031" t="s">
+      <c r="L31" s="988"/>
+      <c r="M31" s="993"/>
+      <c r="N31" s="1022" t="s">
         <v>326</v>
       </c>
       <c r="O31" s="64"/>
@@ -21138,16 +21140,16 @@
       <c r="T31" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U31" s="1012"/>
-      <c r="V31" s="1015"/>
-      <c r="W31" s="986"/>
-      <c r="X31" s="987"/>
-      <c r="Y31" s="982"/>
+      <c r="U31" s="1002"/>
+      <c r="V31" s="1005"/>
+      <c r="W31" s="1032"/>
+      <c r="X31" s="1033"/>
+      <c r="Y31" s="1028"/>
     </row>
     <row r="32" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="L32" s="1037"/>
-      <c r="M32" s="1004"/>
-      <c r="N32" s="1025"/>
+      <c r="L32" s="989"/>
+      <c r="M32" s="993"/>
+      <c r="N32" s="1016"/>
       <c r="O32" s="110"/>
       <c r="P32" s="111"/>
       <c r="Q32" s="112" t="s">
@@ -21158,18 +21160,18 @@
       <c r="T32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U32" s="1012"/>
-      <c r="V32" s="1015"/>
-      <c r="W32" s="986"/>
-      <c r="X32" s="987"/>
-      <c r="Y32" s="982"/>
+      <c r="U32" s="1002"/>
+      <c r="V32" s="1005"/>
+      <c r="W32" s="1032"/>
+      <c r="X32" s="1033"/>
+      <c r="Y32" s="1028"/>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="L33" s="1035" t="s">
+      <c r="L33" s="987" t="s">
         <v>104</v>
       </c>
-      <c r="M33" s="1004"/>
-      <c r="N33" s="1025"/>
+      <c r="M33" s="993"/>
+      <c r="N33" s="1016"/>
       <c r="O33" s="61"/>
       <c r="P33" s="62"/>
       <c r="Q33" s="62"/>
@@ -21180,16 +21182,16 @@
       <c r="T33" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U33" s="1012"/>
-      <c r="V33" s="1015"/>
-      <c r="W33" s="986"/>
-      <c r="X33" s="987"/>
-      <c r="Y33" s="982"/>
+      <c r="U33" s="1002"/>
+      <c r="V33" s="1005"/>
+      <c r="W33" s="1032"/>
+      <c r="X33" s="1033"/>
+      <c r="Y33" s="1028"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="L34" s="1036"/>
-      <c r="M34" s="1004"/>
-      <c r="N34" s="1026"/>
+      <c r="L34" s="988"/>
+      <c r="M34" s="993"/>
+      <c r="N34" s="1017"/>
       <c r="O34" s="64"/>
       <c r="P34" s="65"/>
       <c r="Q34" s="65"/>
@@ -21198,19 +21200,19 @@
       <c r="T34" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U34" s="1012"/>
-      <c r="V34" s="1015"/>
-      <c r="W34" s="986"/>
-      <c r="X34" s="987"/>
-      <c r="Y34" s="982"/>
+      <c r="U34" s="1002"/>
+      <c r="V34" s="1005"/>
+      <c r="W34" s="1032"/>
+      <c r="X34" s="1033"/>
+      <c r="Y34" s="1028"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1520</v>
       </c>
-      <c r="L35" s="1036"/>
-      <c r="M35" s="1004"/>
-      <c r="N35" s="1030" t="s">
+      <c r="L35" s="988"/>
+      <c r="M35" s="993"/>
+      <c r="N35" s="1021" t="s">
         <v>325</v>
       </c>
       <c r="O35" s="64"/>
@@ -21221,20 +21223,20 @@
       <c r="T35" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U35" s="1012"/>
-      <c r="V35" s="1015"/>
-      <c r="W35" s="986"/>
-      <c r="X35" s="987"/>
-      <c r="Y35" s="982"/>
+      <c r="U35" s="1002"/>
+      <c r="V35" s="1005"/>
+      <c r="W35" s="1032"/>
+      <c r="X35" s="1033"/>
+      <c r="Y35" s="1028"/>
       <c r="Z35" s="201"/>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1523</v>
       </c>
-      <c r="L36" s="1037"/>
-      <c r="M36" s="1004"/>
-      <c r="N36" s="1023"/>
+      <c r="L36" s="989"/>
+      <c r="M36" s="993"/>
+      <c r="N36" s="1014"/>
       <c r="O36" s="67" t="s">
         <v>73</v>
       </c>
@@ -21249,22 +21251,22 @@
       <c r="T36" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="U36" s="1012"/>
-      <c r="V36" s="1015"/>
-      <c r="W36" s="986"/>
-      <c r="X36" s="987"/>
-      <c r="Y36" s="982"/>
+      <c r="U36" s="1002"/>
+      <c r="V36" s="1005"/>
+      <c r="W36" s="1032"/>
+      <c r="X36" s="1033"/>
+      <c r="Y36" s="1028"/>
       <c r="Z36" s="202"/>
     </row>
     <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1522</v>
       </c>
-      <c r="L37" s="1035" t="s">
+      <c r="L37" s="987" t="s">
         <v>103</v>
       </c>
-      <c r="M37" s="1004"/>
-      <c r="N37" s="1027" t="s">
+      <c r="M37" s="993"/>
+      <c r="N37" s="1018" t="s">
         <v>310</v>
       </c>
       <c r="O37" s="70"/>
@@ -21281,17 +21283,17 @@
       <c r="T37" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="U37" s="1012"/>
-      <c r="V37" s="1015"/>
-      <c r="W37" s="986"/>
-      <c r="X37" s="987"/>
-      <c r="Y37" s="982"/>
+      <c r="U37" s="1002"/>
+      <c r="V37" s="1005"/>
+      <c r="W37" s="1032"/>
+      <c r="X37" s="1033"/>
+      <c r="Y37" s="1028"/>
       <c r="Z37" s="202"/>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="L38" s="1036"/>
-      <c r="M38" s="1004"/>
-      <c r="N38" s="1028"/>
+      <c r="L38" s="988"/>
+      <c r="M38" s="993"/>
+      <c r="N38" s="1019"/>
       <c r="O38" s="72"/>
       <c r="P38" s="73"/>
       <c r="Q38" s="74" t="s">
@@ -21304,20 +21306,20 @@
       <c r="T38" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U38" s="1012"/>
-      <c r="V38" s="1015"/>
-      <c r="W38" s="986"/>
-      <c r="X38" s="987"/>
-      <c r="Y38" s="982"/>
+      <c r="U38" s="1002"/>
+      <c r="V38" s="1005"/>
+      <c r="W38" s="1032"/>
+      <c r="X38" s="1033"/>
+      <c r="Y38" s="1028"/>
       <c r="Z38" s="202"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1526</v>
       </c>
-      <c r="L39" s="1036"/>
-      <c r="M39" s="1004"/>
-      <c r="N39" s="1028"/>
+      <c r="L39" s="988"/>
+      <c r="M39" s="993"/>
+      <c r="N39" s="1019"/>
       <c r="O39" s="72"/>
       <c r="P39" s="73"/>
       <c r="Q39" s="74" t="s">
@@ -21330,19 +21332,19 @@
       <c r="T39" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U39" s="1012"/>
-      <c r="V39" s="1015"/>
-      <c r="W39" s="986"/>
-      <c r="X39" s="987"/>
-      <c r="Y39" s="982"/>
+      <c r="U39" s="1002"/>
+      <c r="V39" s="1005"/>
+      <c r="W39" s="1032"/>
+      <c r="X39" s="1033"/>
+      <c r="Y39" s="1028"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1527</v>
       </c>
-      <c r="L40" s="1037"/>
-      <c r="M40" s="1004"/>
-      <c r="N40" s="1028"/>
+      <c r="L40" s="989"/>
+      <c r="M40" s="993"/>
+      <c r="N40" s="1019"/>
       <c r="O40" s="96"/>
       <c r="P40" s="97"/>
       <c r="Q40" s="169" t="s">
@@ -21357,19 +21359,19 @@
       <c r="T40" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U40" s="1012"/>
-      <c r="V40" s="1015"/>
-      <c r="W40" s="986"/>
-      <c r="X40" s="987"/>
-      <c r="Y40" s="982"/>
+      <c r="U40" s="1002"/>
+      <c r="V40" s="1005"/>
+      <c r="W40" s="1032"/>
+      <c r="X40" s="1033"/>
+      <c r="Y40" s="1028"/>
       <c r="Z40" s="201"/>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="L41" s="1035" t="s">
+      <c r="L41" s="987" t="s">
         <v>102</v>
       </c>
-      <c r="M41" s="1004"/>
-      <c r="N41" s="1028"/>
+      <c r="M41" s="993"/>
+      <c r="N41" s="1019"/>
       <c r="O41" s="101"/>
       <c r="P41" s="102"/>
       <c r="Q41" s="103" t="s">
@@ -21384,20 +21386,20 @@
       <c r="T41" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U41" s="1012"/>
-      <c r="V41" s="1015"/>
-      <c r="W41" s="986"/>
-      <c r="X41" s="987"/>
-      <c r="Y41" s="982"/>
+      <c r="U41" s="1002"/>
+      <c r="V41" s="1005"/>
+      <c r="W41" s="1032"/>
+      <c r="X41" s="1033"/>
+      <c r="Y41" s="1028"/>
       <c r="Z41" s="202"/>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1521</v>
       </c>
-      <c r="L42" s="1036"/>
-      <c r="M42" s="1004"/>
-      <c r="N42" s="1028"/>
+      <c r="L42" s="988"/>
+      <c r="M42" s="993"/>
+      <c r="N42" s="1019"/>
       <c r="O42" s="72"/>
       <c r="P42" s="73"/>
       <c r="Q42" s="74" t="s">
@@ -21410,19 +21412,19 @@
       <c r="T42" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U42" s="1012"/>
-      <c r="V42" s="1015"/>
-      <c r="W42" s="986"/>
-      <c r="X42" s="987"/>
-      <c r="Y42" s="982"/>
+      <c r="U42" s="1002"/>
+      <c r="V42" s="1005"/>
+      <c r="W42" s="1032"/>
+      <c r="X42" s="1033"/>
+      <c r="Y42" s="1028"/>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1524</v>
       </c>
-      <c r="L43" s="1036"/>
-      <c r="M43" s="1004"/>
-      <c r="N43" s="1028"/>
+      <c r="L43" s="988"/>
+      <c r="M43" s="993"/>
+      <c r="N43" s="1019"/>
       <c r="O43" s="96"/>
       <c r="P43" s="97"/>
       <c r="Q43" s="169" t="s">
@@ -21435,16 +21437,16 @@
       <c r="T43" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U43" s="1012"/>
-      <c r="V43" s="1015"/>
-      <c r="W43" s="986"/>
-      <c r="X43" s="987"/>
-      <c r="Y43" s="982"/>
+      <c r="U43" s="1002"/>
+      <c r="V43" s="1005"/>
+      <c r="W43" s="1032"/>
+      <c r="X43" s="1033"/>
+      <c r="Y43" s="1028"/>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="L44" s="1037"/>
-      <c r="M44" s="1004"/>
-      <c r="N44" s="1028"/>
+      <c r="L44" s="989"/>
+      <c r="M44" s="993"/>
+      <c r="N44" s="1019"/>
       <c r="O44" s="104"/>
       <c r="P44" s="105"/>
       <c r="Q44" s="170" t="s">
@@ -21457,11 +21459,11 @@
       <c r="T44" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U44" s="1012"/>
-      <c r="V44" s="1015"/>
-      <c r="W44" s="986"/>
-      <c r="X44" s="987"/>
-      <c r="Y44" s="982"/>
+      <c r="U44" s="1002"/>
+      <c r="V44" s="1005"/>
+      <c r="W44" s="1032"/>
+      <c r="X44" s="1033"/>
+      <c r="Y44" s="1028"/>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -21473,11 +21475,11 @@
       <c r="C45" t="s">
         <v>1530</v>
       </c>
-      <c r="L45" s="1035" t="s">
+      <c r="L45" s="987" t="s">
         <v>101</v>
       </c>
-      <c r="M45" s="1004"/>
-      <c r="N45" s="1028"/>
+      <c r="M45" s="993"/>
+      <c r="N45" s="1019"/>
       <c r="O45" s="98"/>
       <c r="P45" s="99"/>
       <c r="Q45" s="100" t="s">
@@ -21490,11 +21492,11 @@
       <c r="T45" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U45" s="1012"/>
-      <c r="V45" s="1015"/>
-      <c r="W45" s="986"/>
-      <c r="X45" s="987"/>
-      <c r="Y45" s="982"/>
+      <c r="U45" s="1002"/>
+      <c r="V45" s="1005"/>
+      <c r="W45" s="1032"/>
+      <c r="X45" s="1033"/>
+      <c r="Y45" s="1028"/>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -21509,9 +21511,9 @@
       <c r="D46" s="173" t="s">
         <v>1531</v>
       </c>
-      <c r="L46" s="1038"/>
-      <c r="M46" s="1004"/>
-      <c r="N46" s="1028"/>
+      <c r="L46" s="990"/>
+      <c r="M46" s="993"/>
+      <c r="N46" s="1019"/>
       <c r="O46" s="72"/>
       <c r="P46" s="73"/>
       <c r="Q46" s="74" t="s">
@@ -21524,16 +21526,16 @@
       <c r="T46" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U46" s="1012"/>
-      <c r="V46" s="1015"/>
-      <c r="W46" s="986"/>
-      <c r="X46" s="987"/>
-      <c r="Y46" s="982"/>
+      <c r="U46" s="1002"/>
+      <c r="V46" s="1005"/>
+      <c r="W46" s="1032"/>
+      <c r="X46" s="1033"/>
+      <c r="Y46" s="1028"/>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="L47" s="1038"/>
-      <c r="M47" s="1004"/>
-      <c r="N47" s="1028"/>
+      <c r="L47" s="990"/>
+      <c r="M47" s="993"/>
+      <c r="N47" s="1019"/>
       <c r="O47" s="96"/>
       <c r="P47" s="97"/>
       <c r="Q47" s="169" t="s">
@@ -21546,16 +21548,16 @@
       <c r="T47" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U47" s="1012"/>
-      <c r="V47" s="1015"/>
-      <c r="W47" s="986"/>
-      <c r="X47" s="987"/>
-      <c r="Y47" s="982"/>
+      <c r="U47" s="1002"/>
+      <c r="V47" s="1005"/>
+      <c r="W47" s="1032"/>
+      <c r="X47" s="1033"/>
+      <c r="Y47" s="1028"/>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="L48" s="1039"/>
-      <c r="M48" s="1004"/>
-      <c r="N48" s="1028"/>
+      <c r="L48" s="991"/>
+      <c r="M48" s="993"/>
+      <c r="N48" s="1019"/>
       <c r="O48" s="104"/>
       <c r="P48" s="105"/>
       <c r="Q48" s="170" t="s">
@@ -21568,18 +21570,18 @@
       <c r="T48" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U48" s="1012"/>
-      <c r="V48" s="1015"/>
-      <c r="W48" s="986"/>
-      <c r="X48" s="987"/>
-      <c r="Y48" s="982"/>
+      <c r="U48" s="1002"/>
+      <c r="V48" s="1005"/>
+      <c r="W48" s="1032"/>
+      <c r="X48" s="1033"/>
+      <c r="Y48" s="1028"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L49" s="1035" t="s">
+      <c r="L49" s="987" t="s">
         <v>100</v>
       </c>
-      <c r="M49" s="1004"/>
-      <c r="N49" s="1028"/>
+      <c r="M49" s="993"/>
+      <c r="N49" s="1019"/>
       <c r="O49" s="98"/>
       <c r="P49" s="99"/>
       <c r="Q49" s="100" t="s">
@@ -21592,16 +21594,16 @@
       <c r="T49" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U49" s="1012"/>
-      <c r="V49" s="1015"/>
-      <c r="W49" s="986"/>
-      <c r="X49" s="987"/>
-      <c r="Y49" s="982"/>
+      <c r="U49" s="1002"/>
+      <c r="V49" s="1005"/>
+      <c r="W49" s="1032"/>
+      <c r="X49" s="1033"/>
+      <c r="Y49" s="1028"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L50" s="1036"/>
-      <c r="M50" s="1004"/>
-      <c r="N50" s="1028"/>
+      <c r="L50" s="988"/>
+      <c r="M50" s="993"/>
+      <c r="N50" s="1019"/>
       <c r="O50" s="72"/>
       <c r="P50" s="73"/>
       <c r="Q50" s="74" t="s">
@@ -21610,25 +21612,25 @@
       <c r="R50" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="S50" s="1008" t="s">
+      <c r="S50" s="998" t="s">
         <v>115</v>
       </c>
       <c r="T50" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U50" s="1012"/>
-      <c r="V50" s="1015"/>
-      <c r="W50" s="986"/>
-      <c r="X50" s="987"/>
-      <c r="Y50" s="982"/>
+      <c r="U50" s="1002"/>
+      <c r="V50" s="1005"/>
+      <c r="W50" s="1032"/>
+      <c r="X50" s="1033"/>
+      <c r="Y50" s="1028"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1532</v>
       </c>
-      <c r="L51" s="1036"/>
-      <c r="M51" s="1004"/>
-      <c r="N51" s="1028"/>
+      <c r="L51" s="988"/>
+      <c r="M51" s="993"/>
+      <c r="N51" s="1019"/>
       <c r="O51" s="72"/>
       <c r="P51" s="73"/>
       <c r="Q51" s="74" t="s">
@@ -21637,23 +21639,23 @@
       <c r="R51" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="S51" s="1009"/>
+      <c r="S51" s="999"/>
       <c r="T51" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U51" s="1012"/>
-      <c r="V51" s="1015"/>
-      <c r="W51" s="986"/>
-      <c r="X51" s="987"/>
-      <c r="Y51" s="982"/>
+      <c r="U51" s="1002"/>
+      <c r="V51" s="1005"/>
+      <c r="W51" s="1032"/>
+      <c r="X51" s="1033"/>
+      <c r="Y51" s="1028"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1533</v>
       </c>
-      <c r="L52" s="1037"/>
-      <c r="M52" s="1004"/>
-      <c r="N52" s="1028"/>
+      <c r="L52" s="989"/>
+      <c r="M52" s="993"/>
+      <c r="N52" s="1019"/>
       <c r="O52" s="75" t="s">
         <v>64</v>
       </c>
@@ -21664,22 +21666,22 @@
       <c r="R52" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="S52" s="1010"/>
+      <c r="S52" s="1000"/>
       <c r="T52" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="1012"/>
-      <c r="V52" s="1015"/>
-      <c r="W52" s="986"/>
-      <c r="X52" s="987"/>
-      <c r="Y52" s="982"/>
+      <c r="U52" s="1002"/>
+      <c r="V52" s="1005"/>
+      <c r="W52" s="1032"/>
+      <c r="X52" s="1033"/>
+      <c r="Y52" s="1028"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L53" s="1035" t="s">
+      <c r="L53" s="987" t="s">
         <v>99</v>
       </c>
-      <c r="M53" s="1004"/>
-      <c r="N53" s="1028"/>
+      <c r="M53" s="993"/>
+      <c r="N53" s="1019"/>
       <c r="O53" s="83"/>
       <c r="P53" s="84"/>
       <c r="Q53" s="85" t="s">
@@ -21692,16 +21694,16 @@
       <c r="T53" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="U53" s="1012"/>
-      <c r="V53" s="1015"/>
-      <c r="W53" s="986"/>
-      <c r="X53" s="987"/>
-      <c r="Y53" s="982"/>
+      <c r="U53" s="1002"/>
+      <c r="V53" s="1005"/>
+      <c r="W53" s="1032"/>
+      <c r="X53" s="1033"/>
+      <c r="Y53" s="1028"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L54" s="1036"/>
-      <c r="M54" s="1004"/>
-      <c r="N54" s="1028"/>
+      <c r="L54" s="988"/>
+      <c r="M54" s="993"/>
+      <c r="N54" s="1019"/>
       <c r="O54" s="86"/>
       <c r="P54" s="87"/>
       <c r="Q54" s="88" t="s">
@@ -21714,16 +21716,16 @@
       <c r="T54" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U54" s="1012"/>
-      <c r="V54" s="1015"/>
-      <c r="W54" s="986"/>
-      <c r="X54" s="987"/>
-      <c r="Y54" s="982"/>
+      <c r="U54" s="1002"/>
+      <c r="V54" s="1005"/>
+      <c r="W54" s="1032"/>
+      <c r="X54" s="1033"/>
+      <c r="Y54" s="1028"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L55" s="1036"/>
-      <c r="M55" s="1004"/>
-      <c r="N55" s="1028"/>
+      <c r="L55" s="988"/>
+      <c r="M55" s="993"/>
+      <c r="N55" s="1019"/>
       <c r="O55" s="86"/>
       <c r="P55" s="87"/>
       <c r="Q55" s="88" t="s">
@@ -21736,16 +21738,16 @@
       <c r="T55" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U55" s="1012"/>
-      <c r="V55" s="1015"/>
-      <c r="W55" s="986"/>
-      <c r="X55" s="987"/>
-      <c r="Y55" s="982"/>
+      <c r="U55" s="1002"/>
+      <c r="V55" s="1005"/>
+      <c r="W55" s="1032"/>
+      <c r="X55" s="1033"/>
+      <c r="Y55" s="1028"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L56" s="1037"/>
-      <c r="M56" s="1004"/>
-      <c r="N56" s="1028"/>
+      <c r="L56" s="989"/>
+      <c r="M56" s="993"/>
+      <c r="N56" s="1019"/>
       <c r="O56" s="89" t="s">
         <v>54</v>
       </c>
@@ -21762,18 +21764,18 @@
       <c r="T56" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="U56" s="1012"/>
-      <c r="V56" s="1015"/>
-      <c r="W56" s="986"/>
-      <c r="X56" s="987"/>
-      <c r="Y56" s="982"/>
+      <c r="U56" s="1002"/>
+      <c r="V56" s="1005"/>
+      <c r="W56" s="1032"/>
+      <c r="X56" s="1033"/>
+      <c r="Y56" s="1028"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L57" s="1035" t="s">
+      <c r="L57" s="987" t="s">
         <v>98</v>
       </c>
-      <c r="M57" s="1004"/>
-      <c r="N57" s="1028"/>
+      <c r="M57" s="993"/>
+      <c r="N57" s="1019"/>
       <c r="O57" s="52"/>
       <c r="P57" s="53"/>
       <c r="Q57" s="54" t="s">
@@ -21786,16 +21788,16 @@
       <c r="T57" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="U57" s="1012"/>
-      <c r="V57" s="1015"/>
-      <c r="W57" s="986"/>
-      <c r="X57" s="987"/>
-      <c r="Y57" s="982"/>
+      <c r="U57" s="1002"/>
+      <c r="V57" s="1005"/>
+      <c r="W57" s="1032"/>
+      <c r="X57" s="1033"/>
+      <c r="Y57" s="1028"/>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L58" s="1036"/>
-      <c r="M58" s="1004"/>
-      <c r="N58" s="1028"/>
+      <c r="L58" s="988"/>
+      <c r="M58" s="993"/>
+      <c r="N58" s="1019"/>
       <c r="O58" s="55"/>
       <c r="P58" s="56"/>
       <c r="Q58" s="57" t="s">
@@ -21808,16 +21810,16 @@
       <c r="T58" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="U58" s="1012"/>
-      <c r="V58" s="1015"/>
-      <c r="W58" s="986"/>
-      <c r="X58" s="987"/>
-      <c r="Y58" s="982"/>
+      <c r="U58" s="1002"/>
+      <c r="V58" s="1005"/>
+      <c r="W58" s="1032"/>
+      <c r="X58" s="1033"/>
+      <c r="Y58" s="1028"/>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L59" s="1036"/>
-      <c r="M59" s="1004"/>
-      <c r="N59" s="1028"/>
+      <c r="L59" s="988"/>
+      <c r="M59" s="993"/>
+      <c r="N59" s="1019"/>
       <c r="O59" s="55"/>
       <c r="P59" s="56"/>
       <c r="Q59" s="57" t="s">
@@ -21830,16 +21832,16 @@
       <c r="T59" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U59" s="1012"/>
-      <c r="V59" s="1015"/>
-      <c r="W59" s="986"/>
-      <c r="X59" s="987"/>
-      <c r="Y59" s="982"/>
+      <c r="U59" s="1002"/>
+      <c r="V59" s="1005"/>
+      <c r="W59" s="1032"/>
+      <c r="X59" s="1033"/>
+      <c r="Y59" s="1028"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L60" s="1037"/>
-      <c r="M60" s="1004"/>
-      <c r="N60" s="1028"/>
+      <c r="L60" s="989"/>
+      <c r="M60" s="993"/>
+      <c r="N60" s="1019"/>
       <c r="O60" s="55"/>
       <c r="P60" s="56"/>
       <c r="Q60" s="57" t="s">
@@ -21852,18 +21854,18 @@
       <c r="T60" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U60" s="1012"/>
-      <c r="V60" s="1015"/>
-      <c r="W60" s="986"/>
-      <c r="X60" s="987"/>
-      <c r="Y60" s="982"/>
+      <c r="U60" s="1002"/>
+      <c r="V60" s="1005"/>
+      <c r="W60" s="1032"/>
+      <c r="X60" s="1033"/>
+      <c r="Y60" s="1028"/>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L61" s="1035" t="s">
+      <c r="L61" s="987" t="s">
         <v>97</v>
       </c>
-      <c r="M61" s="1004"/>
-      <c r="N61" s="1028"/>
+      <c r="M61" s="993"/>
+      <c r="N61" s="1019"/>
       <c r="O61" s="55"/>
       <c r="P61" s="56"/>
       <c r="Q61" s="57" t="s">
@@ -21876,16 +21878,16 @@
       <c r="T61" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U61" s="1012"/>
-      <c r="V61" s="1015"/>
-      <c r="W61" s="986"/>
-      <c r="X61" s="987"/>
-      <c r="Y61" s="982"/>
+      <c r="U61" s="1002"/>
+      <c r="V61" s="1005"/>
+      <c r="W61" s="1032"/>
+      <c r="X61" s="1033"/>
+      <c r="Y61" s="1028"/>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L62" s="1036"/>
-      <c r="M62" s="1004"/>
-      <c r="N62" s="1028"/>
+      <c r="L62" s="988"/>
+      <c r="M62" s="993"/>
+      <c r="N62" s="1019"/>
       <c r="O62" s="55"/>
       <c r="P62" s="56"/>
       <c r="Q62" s="57" t="s">
@@ -21898,16 +21900,16 @@
       <c r="T62" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U62" s="1012"/>
-      <c r="V62" s="1015"/>
-      <c r="W62" s="986"/>
-      <c r="X62" s="987"/>
-      <c r="Y62" s="982"/>
+      <c r="U62" s="1002"/>
+      <c r="V62" s="1005"/>
+      <c r="W62" s="1032"/>
+      <c r="X62" s="1033"/>
+      <c r="Y62" s="1028"/>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L63" s="1036"/>
-      <c r="M63" s="1004"/>
-      <c r="N63" s="1028"/>
+      <c r="L63" s="988"/>
+      <c r="M63" s="993"/>
+      <c r="N63" s="1019"/>
       <c r="O63" s="55"/>
       <c r="P63" s="56"/>
       <c r="Q63" s="57" t="s">
@@ -21920,16 +21922,16 @@
       <c r="T63" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U63" s="1012"/>
-      <c r="V63" s="1015"/>
-      <c r="W63" s="986"/>
-      <c r="X63" s="987"/>
-      <c r="Y63" s="982"/>
+      <c r="U63" s="1002"/>
+      <c r="V63" s="1005"/>
+      <c r="W63" s="1032"/>
+      <c r="X63" s="1033"/>
+      <c r="Y63" s="1028"/>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="L64" s="1037"/>
-      <c r="M64" s="1004"/>
-      <c r="N64" s="1028"/>
+      <c r="L64" s="989"/>
+      <c r="M64" s="993"/>
+      <c r="N64" s="1019"/>
       <c r="O64" s="58" t="s">
         <v>36</v>
       </c>
@@ -21946,18 +21948,18 @@
       <c r="T64" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="U64" s="1012"/>
-      <c r="V64" s="1015"/>
-      <c r="W64" s="986"/>
-      <c r="X64" s="987"/>
-      <c r="Y64" s="982"/>
+      <c r="U64" s="1002"/>
+      <c r="V64" s="1005"/>
+      <c r="W64" s="1032"/>
+      <c r="X64" s="1033"/>
+      <c r="Y64" s="1028"/>
     </row>
     <row r="65" spans="12:25" x14ac:dyDescent="0.25">
-      <c r="L65" s="1035" t="s">
+      <c r="L65" s="987" t="s">
         <v>96</v>
       </c>
-      <c r="M65" s="1004"/>
-      <c r="N65" s="1028"/>
+      <c r="M65" s="993"/>
+      <c r="N65" s="1019"/>
       <c r="O65" s="61"/>
       <c r="P65" s="62"/>
       <c r="Q65" s="63" t="s">
@@ -21970,16 +21972,16 @@
       <c r="T65" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="U65" s="1012"/>
-      <c r="V65" s="1015"/>
-      <c r="W65" s="986"/>
-      <c r="X65" s="987"/>
-      <c r="Y65" s="982"/>
+      <c r="U65" s="1002"/>
+      <c r="V65" s="1005"/>
+      <c r="W65" s="1032"/>
+      <c r="X65" s="1033"/>
+      <c r="Y65" s="1028"/>
     </row>
     <row r="66" spans="12:25" x14ac:dyDescent="0.25">
-      <c r="L66" s="1036"/>
-      <c r="M66" s="1004"/>
-      <c r="N66" s="1028"/>
+      <c r="L66" s="988"/>
+      <c r="M66" s="993"/>
+      <c r="N66" s="1019"/>
       <c r="O66" s="64"/>
       <c r="P66" s="65"/>
       <c r="Q66" s="66" t="s">
@@ -21992,16 +21994,16 @@
       <c r="T66" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U66" s="1012"/>
-      <c r="V66" s="1015"/>
-      <c r="W66" s="986"/>
-      <c r="X66" s="987"/>
-      <c r="Y66" s="982"/>
+      <c r="U66" s="1002"/>
+      <c r="V66" s="1005"/>
+      <c r="W66" s="1032"/>
+      <c r="X66" s="1033"/>
+      <c r="Y66" s="1028"/>
     </row>
     <row r="67" spans="12:25" x14ac:dyDescent="0.25">
-      <c r="L67" s="1036"/>
-      <c r="M67" s="1004"/>
-      <c r="N67" s="1028"/>
+      <c r="L67" s="988"/>
+      <c r="M67" s="993"/>
+      <c r="N67" s="1019"/>
       <c r="O67" s="64"/>
       <c r="P67" s="65"/>
       <c r="Q67" s="66" t="s">
@@ -22014,16 +22016,16 @@
       <c r="T67" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="U67" s="1012"/>
-      <c r="V67" s="1015"/>
-      <c r="W67" s="986"/>
-      <c r="X67" s="987"/>
-      <c r="Y67" s="982"/>
+      <c r="U67" s="1002"/>
+      <c r="V67" s="1005"/>
+      <c r="W67" s="1032"/>
+      <c r="X67" s="1033"/>
+      <c r="Y67" s="1028"/>
     </row>
     <row r="68" spans="12:25" x14ac:dyDescent="0.25">
-      <c r="L68" s="1037"/>
-      <c r="M68" s="1005"/>
-      <c r="N68" s="1029"/>
+      <c r="L68" s="989"/>
+      <c r="M68" s="994"/>
+      <c r="N68" s="1020"/>
       <c r="O68" s="67" t="s">
         <v>25</v>
       </c>
@@ -22040,11 +22042,11 @@
       <c r="T68" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="U68" s="1013"/>
-      <c r="V68" s="1016"/>
-      <c r="W68" s="988"/>
-      <c r="X68" s="989"/>
-      <c r="Y68" s="983"/>
+      <c r="U68" s="1003"/>
+      <c r="V68" s="1006"/>
+      <c r="W68" s="1034"/>
+      <c r="X68" s="1035"/>
+      <c r="Y68" s="1029"/>
     </row>
     <row r="69" spans="12:25" x14ac:dyDescent="0.25">
       <c r="N69" s="205"/>
@@ -22052,11 +22054,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AC3:AK3"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Y5:Y68"/>
+    <mergeCell ref="W17:X67"/>
+    <mergeCell ref="W68:X68"/>
+    <mergeCell ref="W5:W16"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="M5:M68"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="S50:S52"/>
+    <mergeCell ref="U5:U68"/>
+    <mergeCell ref="V5:V68"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="N8:N11"/>
+    <mergeCell ref="N37:N68"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="N31:N34"/>
+    <mergeCell ref="N26:N30"/>
     <mergeCell ref="L65:L68"/>
     <mergeCell ref="L61:L64"/>
     <mergeCell ref="L57:L60"/>
@@ -22073,34 +22098,11 @@
     <mergeCell ref="L49:L52"/>
     <mergeCell ref="L45:L48"/>
     <mergeCell ref="L41:L44"/>
-    <mergeCell ref="M5:M68"/>
-    <mergeCell ref="O3:T3"/>
-    <mergeCell ref="S50:S52"/>
-    <mergeCell ref="U5:U68"/>
-    <mergeCell ref="V5:V68"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="N8:N11"/>
-    <mergeCell ref="N37:N68"/>
-    <mergeCell ref="N35:N36"/>
-    <mergeCell ref="N31:N34"/>
-    <mergeCell ref="N26:N30"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Y5:Y68"/>
-    <mergeCell ref="W17:X67"/>
-    <mergeCell ref="W68:X68"/>
-    <mergeCell ref="W5:W16"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="X9:X10"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AC3:AK3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22120,18 +22122,18 @@
       <c r="E3" s="466" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="1048" t="s">
+      <c r="F3" s="1071" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="1049"/>
-      <c r="H3" s="1049"/>
-      <c r="I3" s="1049"/>
-      <c r="J3" s="1049"/>
-      <c r="K3" s="1049"/>
-      <c r="L3" s="1067">
+      <c r="G3" s="1072"/>
+      <c r="H3" s="1072"/>
+      <c r="I3" s="1072"/>
+      <c r="J3" s="1072"/>
+      <c r="K3" s="1072"/>
+      <c r="L3" s="1051">
         <v>2</v>
       </c>
-      <c r="M3" s="1069">
+      <c r="M3" s="1053">
         <v>5</v>
       </c>
     </row>
@@ -22155,11 +22157,11 @@
       <c r="K4" s="141" t="s">
         <v>88</v>
       </c>
-      <c r="L4" s="1068"/>
-      <c r="M4" s="1070"/>
+      <c r="L4" s="1052"/>
+      <c r="M4" s="1054"/>
     </row>
     <row r="5" spans="5:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E5" s="1050" t="s">
+      <c r="E5" s="1060" t="s">
         <v>111</v>
       </c>
       <c r="F5" s="920"/>
@@ -22170,13 +22172,13 @@
       <c r="K5" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="1056" t="s">
+      <c r="L5" s="1063" t="s">
         <v>1447</v>
       </c>
       <c r="M5" s="954"/>
     </row>
     <row r="6" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E6" s="1051"/>
+      <c r="E6" s="1061"/>
       <c r="F6" s="406"/>
       <c r="G6" s="924"/>
       <c r="H6" s="924"/>
@@ -22185,11 +22187,11 @@
       <c r="K6" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="1057"/>
+      <c r="L6" s="1064"/>
       <c r="M6" s="955"/>
     </row>
     <row r="7" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E7" s="1051"/>
+      <c r="E7" s="1061"/>
       <c r="F7" s="406"/>
       <c r="G7" s="924"/>
       <c r="H7" s="924"/>
@@ -22198,11 +22200,11 @@
       <c r="K7" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="1057"/>
+      <c r="L7" s="1064"/>
       <c r="M7" s="955"/>
     </row>
     <row r="8" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E8" s="1053"/>
+      <c r="E8" s="1062"/>
       <c r="F8" s="925"/>
       <c r="G8" s="926"/>
       <c r="H8" s="927"/>
@@ -22211,11 +22213,11 @@
       <c r="K8" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="1057"/>
+      <c r="L8" s="1064"/>
       <c r="M8" s="955"/>
     </row>
     <row r="9" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E9" s="1050" t="s">
+      <c r="E9" s="1060" t="s">
         <v>110</v>
       </c>
       <c r="F9" s="920"/>
@@ -22226,11 +22228,11 @@
       <c r="K9" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="1057"/>
+      <c r="L9" s="1064"/>
       <c r="M9" s="955"/>
     </row>
     <row r="10" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E10" s="1051"/>
+      <c r="E10" s="1061"/>
       <c r="F10" s="406"/>
       <c r="G10" s="924"/>
       <c r="H10" s="924"/>
@@ -22239,11 +22241,11 @@
       <c r="K10" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="1057"/>
+      <c r="L10" s="1064"/>
       <c r="M10" s="955"/>
     </row>
     <row r="11" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E11" s="1051"/>
+      <c r="E11" s="1061"/>
       <c r="F11" s="406"/>
       <c r="G11" s="924"/>
       <c r="H11" s="924"/>
@@ -22252,11 +22254,11 @@
       <c r="K11" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L11" s="1057"/>
+      <c r="L11" s="1064"/>
       <c r="M11" s="955"/>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E12" s="1053"/>
+      <c r="E12" s="1062"/>
       <c r="F12" s="930"/>
       <c r="G12" s="931"/>
       <c r="H12" s="932"/>
@@ -22265,11 +22267,11 @@
       <c r="K12" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L12" s="1057"/>
+      <c r="L12" s="1064"/>
       <c r="M12" s="955"/>
     </row>
     <row r="13" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E13" s="1050" t="s">
+      <c r="E13" s="1060" t="s">
         <v>109</v>
       </c>
       <c r="F13" s="933"/>
@@ -22280,11 +22282,11 @@
       <c r="K13" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L13" s="1057"/>
+      <c r="L13" s="1064"/>
       <c r="M13" s="955"/>
     </row>
     <row r="14" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E14" s="1051"/>
+      <c r="E14" s="1061"/>
       <c r="F14" s="406"/>
       <c r="G14" s="924"/>
       <c r="H14" s="924"/>
@@ -22293,11 +22295,11 @@
       <c r="K14" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L14" s="1057"/>
+      <c r="L14" s="1064"/>
       <c r="M14" s="955"/>
     </row>
     <row r="15" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E15" s="1051"/>
+      <c r="E15" s="1061"/>
       <c r="F15" s="406"/>
       <c r="G15" s="924"/>
       <c r="H15" s="924"/>
@@ -22306,11 +22308,11 @@
       <c r="K15" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L15" s="1057"/>
+      <c r="L15" s="1064"/>
       <c r="M15" s="955"/>
     </row>
     <row r="16" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E16" s="1053"/>
+      <c r="E16" s="1062"/>
       <c r="F16" s="925"/>
       <c r="G16" s="926"/>
       <c r="H16" s="927"/>
@@ -22319,11 +22321,11 @@
       <c r="K16" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L16" s="1057"/>
+      <c r="L16" s="1064"/>
       <c r="M16" s="955"/>
     </row>
     <row r="17" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E17" s="1050" t="s">
+      <c r="E17" s="1060" t="s">
         <v>108</v>
       </c>
       <c r="F17" s="920"/>
@@ -22334,11 +22336,11 @@
       <c r="K17" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L17" s="1057"/>
+      <c r="L17" s="1064"/>
       <c r="M17" s="955"/>
     </row>
     <row r="18" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E18" s="1051"/>
+      <c r="E18" s="1061"/>
       <c r="F18" s="406"/>
       <c r="G18" s="924"/>
       <c r="H18" s="924"/>
@@ -22347,11 +22349,11 @@
       <c r="K18" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L18" s="1057"/>
+      <c r="L18" s="1064"/>
       <c r="M18" s="955"/>
     </row>
     <row r="19" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E19" s="1051"/>
+      <c r="E19" s="1061"/>
       <c r="F19" s="406"/>
       <c r="G19" s="924"/>
       <c r="H19" s="924"/>
@@ -22360,11 +22362,11 @@
       <c r="K19" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L19" s="1057"/>
+      <c r="L19" s="1064"/>
       <c r="M19" s="955"/>
     </row>
     <row r="20" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E20" s="1053"/>
+      <c r="E20" s="1062"/>
       <c r="F20" s="930"/>
       <c r="G20" s="931"/>
       <c r="H20" s="932"/>
@@ -22373,11 +22375,11 @@
       <c r="K20" s="688" t="s">
         <v>33</v>
       </c>
-      <c r="L20" s="1057"/>
+      <c r="L20" s="1064"/>
       <c r="M20" s="955"/>
     </row>
     <row r="21" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E21" s="1050" t="s">
+      <c r="E21" s="1060" t="s">
         <v>107</v>
       </c>
       <c r="F21" s="936"/>
@@ -22388,13 +22390,13 @@
       <c r="K21" s="901" t="s">
         <v>33</v>
       </c>
-      <c r="L21" s="1073" t="s">
+      <c r="L21" s="1057" t="s">
         <v>1452</v>
       </c>
       <c r="M21" s="955"/>
     </row>
     <row r="22" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E22" s="1051"/>
+      <c r="E22" s="1061"/>
       <c r="F22" s="406"/>
       <c r="G22" s="924"/>
       <c r="H22" s="924"/>
@@ -22403,11 +22405,11 @@
       <c r="K22" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L22" s="1074"/>
+      <c r="L22" s="1058"/>
       <c r="M22" s="955"/>
     </row>
     <row r="23" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E23" s="1051"/>
+      <c r="E23" s="1061"/>
       <c r="F23" s="930"/>
       <c r="G23" s="931"/>
       <c r="H23" s="931"/>
@@ -22416,11 +22418,11 @@
       <c r="K23" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L23" s="1074"/>
+      <c r="L23" s="1058"/>
       <c r="M23" s="955"/>
     </row>
     <row r="24" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E24" s="1053"/>
+      <c r="E24" s="1062"/>
       <c r="F24" s="925"/>
       <c r="G24" s="926"/>
       <c r="H24" s="927"/>
@@ -22429,11 +22431,11 @@
       <c r="K24" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="1074"/>
+      <c r="L24" s="1058"/>
       <c r="M24" s="955"/>
     </row>
     <row r="25" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E25" s="1050" t="s">
+      <c r="E25" s="1060" t="s">
         <v>106</v>
       </c>
       <c r="F25" s="920"/>
@@ -22444,11 +22446,11 @@
       <c r="K25" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L25" s="1074"/>
+      <c r="L25" s="1058"/>
       <c r="M25" s="955"/>
     </row>
     <row r="26" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E26" s="1051"/>
+      <c r="E26" s="1061"/>
       <c r="F26" s="406"/>
       <c r="G26" s="924"/>
       <c r="H26" s="924"/>
@@ -22457,11 +22459,11 @@
       <c r="K26" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L26" s="1075"/>
+      <c r="L26" s="1059"/>
       <c r="M26" s="955"/>
     </row>
     <row r="27" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E27" s="1051"/>
+      <c r="E27" s="1061"/>
       <c r="F27" s="930"/>
       <c r="G27" s="931"/>
       <c r="H27" s="932" t="s">
@@ -22474,13 +22476,13 @@
       <c r="K27" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L27" s="1071" t="s">
+      <c r="L27" s="1055" t="s">
         <v>1448</v>
       </c>
       <c r="M27" s="955"/>
     </row>
     <row r="28" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E28" s="1053"/>
+      <c r="E28" s="1062"/>
       <c r="F28" s="930"/>
       <c r="G28" s="931"/>
       <c r="H28" s="932" t="s">
@@ -22493,11 +22495,11 @@
       <c r="K28" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L28" s="1072"/>
+      <c r="L28" s="1056"/>
       <c r="M28" s="955"/>
     </row>
     <row r="29" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E29" s="1050" t="s">
+      <c r="E29" s="1060" t="s">
         <v>105</v>
       </c>
       <c r="F29" s="933"/>
@@ -22508,13 +22510,13 @@
       <c r="K29" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L29" s="1058" t="s">
+      <c r="L29" s="1065" t="s">
         <v>1450</v>
       </c>
       <c r="M29" s="955"/>
     </row>
     <row r="30" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E30" s="1051"/>
+      <c r="E30" s="1061"/>
       <c r="F30" s="406"/>
       <c r="G30" s="924"/>
       <c r="H30" s="924"/>
@@ -22523,11 +22525,11 @@
       <c r="K30" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L30" s="1059"/>
+      <c r="L30" s="1066"/>
       <c r="M30" s="955"/>
     </row>
     <row r="31" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E31" s="1051"/>
+      <c r="E31" s="1061"/>
       <c r="F31" s="406"/>
       <c r="G31" s="924"/>
       <c r="H31" s="924"/>
@@ -22536,11 +22538,11 @@
       <c r="K31" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L31" s="1059"/>
+      <c r="L31" s="1066"/>
       <c r="M31" s="955"/>
     </row>
     <row r="32" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E32" s="1053"/>
+      <c r="E32" s="1062"/>
       <c r="F32" s="941"/>
       <c r="G32" s="942"/>
       <c r="H32" s="943"/>
@@ -22549,11 +22551,11 @@
       <c r="K32" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L32" s="1059"/>
+      <c r="L32" s="1066"/>
       <c r="M32" s="955"/>
     </row>
     <row r="33" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E33" s="1050" t="s">
+      <c r="E33" s="1060" t="s">
         <v>104</v>
       </c>
       <c r="F33" s="920"/>
@@ -22564,11 +22566,11 @@
       <c r="K33" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L33" s="1059"/>
+      <c r="L33" s="1066"/>
       <c r="M33" s="955"/>
     </row>
     <row r="34" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E34" s="1051"/>
+      <c r="E34" s="1061"/>
       <c r="F34" s="406"/>
       <c r="G34" s="924"/>
       <c r="H34" s="924"/>
@@ -22577,11 +22579,11 @@
       <c r="K34" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L34" s="1059"/>
+      <c r="L34" s="1066"/>
       <c r="M34" s="955"/>
     </row>
     <row r="35" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E35" s="1051"/>
+      <c r="E35" s="1061"/>
       <c r="F35" s="406"/>
       <c r="G35" s="924"/>
       <c r="H35" s="924"/>
@@ -22590,11 +22592,11 @@
       <c r="K35" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L35" s="1059"/>
+      <c r="L35" s="1066"/>
       <c r="M35" s="955"/>
     </row>
     <row r="36" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E36" s="1053"/>
+      <c r="E36" s="1062"/>
       <c r="F36" s="945"/>
       <c r="G36" s="946"/>
       <c r="H36" s="947"/>
@@ -22603,11 +22605,11 @@
       <c r="K36" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="L36" s="1060"/>
+      <c r="L36" s="1067"/>
       <c r="M36" s="955"/>
     </row>
     <row r="37" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E37" s="1050" t="s">
+      <c r="E37" s="1060" t="s">
         <v>103</v>
       </c>
       <c r="F37" s="70"/>
@@ -22624,15 +22626,15 @@
       <c r="K37" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="L37" s="1061" t="s">
+      <c r="L37" s="1068" t="s">
         <v>1451</v>
       </c>
-      <c r="M37" s="1064" t="s">
+      <c r="M37" s="1048" t="s">
         <v>1449</v>
       </c>
     </row>
     <row r="38" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E38" s="1051"/>
+      <c r="E38" s="1061"/>
       <c r="F38" s="72"/>
       <c r="G38" s="73"/>
       <c r="H38" s="74" t="s">
@@ -22645,11 +22647,11 @@
       <c r="K38" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L38" s="1062"/>
-      <c r="M38" s="1065"/>
+      <c r="L38" s="1069"/>
+      <c r="M38" s="1049"/>
     </row>
     <row r="39" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E39" s="1051"/>
+      <c r="E39" s="1061"/>
       <c r="F39" s="72"/>
       <c r="G39" s="73"/>
       <c r="H39" s="74" t="s">
@@ -22662,11 +22664,11 @@
       <c r="K39" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L39" s="1062"/>
-      <c r="M39" s="1065"/>
+      <c r="L39" s="1069"/>
+      <c r="M39" s="1049"/>
     </row>
     <row r="40" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E40" s="1053"/>
+      <c r="E40" s="1062"/>
       <c r="F40" s="96"/>
       <c r="G40" s="97"/>
       <c r="H40" s="169" t="s">
@@ -22681,11 +22683,11 @@
       <c r="K40" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L40" s="1062"/>
-      <c r="M40" s="1065"/>
+      <c r="L40" s="1069"/>
+      <c r="M40" s="1049"/>
     </row>
     <row r="41" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E41" s="1050" t="s">
+      <c r="E41" s="1060" t="s">
         <v>102</v>
       </c>
       <c r="F41" s="101"/>
@@ -22702,11 +22704,11 @@
       <c r="K41" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L41" s="1062"/>
-      <c r="M41" s="1065"/>
+      <c r="L41" s="1069"/>
+      <c r="M41" s="1049"/>
     </row>
     <row r="42" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E42" s="1051"/>
+      <c r="E42" s="1061"/>
       <c r="F42" s="72"/>
       <c r="G42" s="73"/>
       <c r="H42" s="74" t="s">
@@ -22719,11 +22721,11 @@
       <c r="K42" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L42" s="1062"/>
-      <c r="M42" s="1065"/>
+      <c r="L42" s="1069"/>
+      <c r="M42" s="1049"/>
     </row>
     <row r="43" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E43" s="1051"/>
+      <c r="E43" s="1061"/>
       <c r="F43" s="96"/>
       <c r="G43" s="97"/>
       <c r="H43" s="169" t="s">
@@ -22736,11 +22738,11 @@
       <c r="K43" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L43" s="1062"/>
-      <c r="M43" s="1065"/>
+      <c r="L43" s="1069"/>
+      <c r="M43" s="1049"/>
     </row>
     <row r="44" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E44" s="1053"/>
+      <c r="E44" s="1062"/>
       <c r="F44" s="104"/>
       <c r="G44" s="105"/>
       <c r="H44" s="170" t="s">
@@ -22753,11 +22755,11 @@
       <c r="K44" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L44" s="1062"/>
-      <c r="M44" s="1065"/>
+      <c r="L44" s="1069"/>
+      <c r="M44" s="1049"/>
     </row>
     <row r="45" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E45" s="1050" t="s">
+      <c r="E45" s="1060" t="s">
         <v>101</v>
       </c>
       <c r="F45" s="98"/>
@@ -22772,11 +22774,11 @@
       <c r="K45" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L45" s="1062"/>
-      <c r="M45" s="1065"/>
+      <c r="L45" s="1069"/>
+      <c r="M45" s="1049"/>
     </row>
     <row r="46" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E46" s="1054"/>
+      <c r="E46" s="1074"/>
       <c r="F46" s="72"/>
       <c r="G46" s="73"/>
       <c r="H46" s="74" t="s">
@@ -22789,11 +22791,11 @@
       <c r="K46" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L46" s="1062"/>
-      <c r="M46" s="1065"/>
+      <c r="L46" s="1069"/>
+      <c r="M46" s="1049"/>
     </row>
     <row r="47" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E47" s="1054"/>
+      <c r="E47" s="1074"/>
       <c r="F47" s="96"/>
       <c r="G47" s="97"/>
       <c r="H47" s="169" t="s">
@@ -22806,11 +22808,11 @@
       <c r="K47" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L47" s="1062"/>
-      <c r="M47" s="1065"/>
+      <c r="L47" s="1069"/>
+      <c r="M47" s="1049"/>
     </row>
     <row r="48" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E48" s="1055"/>
+      <c r="E48" s="1075"/>
       <c r="F48" s="104"/>
       <c r="G48" s="105"/>
       <c r="H48" s="170" t="s">
@@ -22823,11 +22825,11 @@
       <c r="K48" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L48" s="1062"/>
-      <c r="M48" s="1065"/>
+      <c r="L48" s="1069"/>
+      <c r="M48" s="1049"/>
     </row>
     <row r="49" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E49" s="1050" t="s">
+      <c r="E49" s="1060" t="s">
         <v>100</v>
       </c>
       <c r="F49" s="98"/>
@@ -22842,11 +22844,11 @@
       <c r="K49" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L49" s="1062"/>
-      <c r="M49" s="1065"/>
+      <c r="L49" s="1069"/>
+      <c r="M49" s="1049"/>
     </row>
     <row r="50" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E50" s="1051"/>
+      <c r="E50" s="1061"/>
       <c r="F50" s="72"/>
       <c r="G50" s="73"/>
       <c r="H50" s="74" t="s">
@@ -22855,17 +22857,17 @@
       <c r="I50" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="J50" s="1008" t="s">
+      <c r="J50" s="998" t="s">
         <v>115</v>
       </c>
       <c r="K50" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L50" s="1062"/>
-      <c r="M50" s="1065"/>
+      <c r="L50" s="1069"/>
+      <c r="M50" s="1049"/>
     </row>
     <row r="51" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E51" s="1051"/>
+      <c r="E51" s="1061"/>
       <c r="F51" s="72"/>
       <c r="G51" s="73"/>
       <c r="H51" s="74" t="s">
@@ -22874,15 +22876,15 @@
       <c r="I51" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="J51" s="1009"/>
+      <c r="J51" s="999"/>
       <c r="K51" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L51" s="1062"/>
-      <c r="M51" s="1065"/>
+      <c r="L51" s="1069"/>
+      <c r="M51" s="1049"/>
     </row>
     <row r="52" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E52" s="1053"/>
+      <c r="E52" s="1062"/>
       <c r="F52" s="75" t="s">
         <v>64</v>
       </c>
@@ -22893,15 +22895,15 @@
       <c r="I52" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="J52" s="1010"/>
+      <c r="J52" s="1000"/>
       <c r="K52" s="951" t="s">
         <v>32</v>
       </c>
-      <c r="L52" s="1062"/>
-      <c r="M52" s="1065"/>
+      <c r="L52" s="1069"/>
+      <c r="M52" s="1049"/>
     </row>
     <row r="53" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E53" s="1050" t="s">
+      <c r="E53" s="1060" t="s">
         <v>99</v>
       </c>
       <c r="F53" s="83"/>
@@ -22916,11 +22918,11 @@
       <c r="K53" s="901" t="s">
         <v>33</v>
       </c>
-      <c r="L53" s="1062"/>
-      <c r="M53" s="1065"/>
+      <c r="L53" s="1069"/>
+      <c r="M53" s="1049"/>
     </row>
     <row r="54" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E54" s="1051"/>
+      <c r="E54" s="1061"/>
       <c r="F54" s="86"/>
       <c r="G54" s="87"/>
       <c r="H54" s="88" t="s">
@@ -22933,11 +22935,11 @@
       <c r="K54" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L54" s="1062"/>
-      <c r="M54" s="1065"/>
+      <c r="L54" s="1069"/>
+      <c r="M54" s="1049"/>
     </row>
     <row r="55" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E55" s="1051"/>
+      <c r="E55" s="1061"/>
       <c r="F55" s="86"/>
       <c r="G55" s="87"/>
       <c r="H55" s="88" t="s">
@@ -22950,11 +22952,11 @@
       <c r="K55" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L55" s="1062"/>
-      <c r="M55" s="1065"/>
+      <c r="L55" s="1069"/>
+      <c r="M55" s="1049"/>
     </row>
     <row r="56" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E56" s="1053"/>
+      <c r="E56" s="1062"/>
       <c r="F56" s="89" t="s">
         <v>54</v>
       </c>
@@ -22971,11 +22973,11 @@
       <c r="K56" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="L56" s="1062"/>
-      <c r="M56" s="1065"/>
+      <c r="L56" s="1069"/>
+      <c r="M56" s="1049"/>
     </row>
     <row r="57" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E57" s="1050" t="s">
+      <c r="E57" s="1060" t="s">
         <v>98</v>
       </c>
       <c r="F57" s="52"/>
@@ -22990,11 +22992,11 @@
       <c r="K57" s="901" t="s">
         <v>33</v>
       </c>
-      <c r="L57" s="1062"/>
-      <c r="M57" s="1065"/>
+      <c r="L57" s="1069"/>
+      <c r="M57" s="1049"/>
     </row>
     <row r="58" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E58" s="1051"/>
+      <c r="E58" s="1061"/>
       <c r="F58" s="55"/>
       <c r="G58" s="56"/>
       <c r="H58" s="57" t="s">
@@ -23007,11 +23009,11 @@
       <c r="K58" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L58" s="1062"/>
-      <c r="M58" s="1065"/>
+      <c r="L58" s="1069"/>
+      <c r="M58" s="1049"/>
     </row>
     <row r="59" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E59" s="1051"/>
+      <c r="E59" s="1061"/>
       <c r="F59" s="55"/>
       <c r="G59" s="56"/>
       <c r="H59" s="57" t="s">
@@ -23024,11 +23026,11 @@
       <c r="K59" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L59" s="1062"/>
-      <c r="M59" s="1065"/>
+      <c r="L59" s="1069"/>
+      <c r="M59" s="1049"/>
     </row>
     <row r="60" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E60" s="1053"/>
+      <c r="E60" s="1062"/>
       <c r="F60" s="55"/>
       <c r="G60" s="56"/>
       <c r="H60" s="57" t="s">
@@ -23041,11 +23043,11 @@
       <c r="K60" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L60" s="1062"/>
-      <c r="M60" s="1065"/>
+      <c r="L60" s="1069"/>
+      <c r="M60" s="1049"/>
     </row>
     <row r="61" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E61" s="1050" t="s">
+      <c r="E61" s="1060" t="s">
         <v>97</v>
       </c>
       <c r="F61" s="55"/>
@@ -23060,11 +23062,11 @@
       <c r="K61" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L61" s="1062"/>
-      <c r="M61" s="1065"/>
+      <c r="L61" s="1069"/>
+      <c r="M61" s="1049"/>
     </row>
     <row r="62" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E62" s="1051"/>
+      <c r="E62" s="1061"/>
       <c r="F62" s="55"/>
       <c r="G62" s="56"/>
       <c r="H62" s="57" t="s">
@@ -23077,11 +23079,11 @@
       <c r="K62" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L62" s="1062"/>
-      <c r="M62" s="1065"/>
+      <c r="L62" s="1069"/>
+      <c r="M62" s="1049"/>
     </row>
     <row r="63" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E63" s="1051"/>
+      <c r="E63" s="1061"/>
       <c r="F63" s="55"/>
       <c r="G63" s="56"/>
       <c r="H63" s="57" t="s">
@@ -23094,11 +23096,11 @@
       <c r="K63" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="L63" s="1062"/>
-      <c r="M63" s="1065"/>
+      <c r="L63" s="1069"/>
+      <c r="M63" s="1049"/>
     </row>
     <row r="64" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E64" s="1053"/>
+      <c r="E64" s="1062"/>
       <c r="F64" s="58" t="s">
         <v>36</v>
       </c>
@@ -23115,11 +23117,11 @@
       <c r="K64" s="951" t="s">
         <v>32</v>
       </c>
-      <c r="L64" s="1063"/>
-      <c r="M64" s="1066"/>
+      <c r="L64" s="1070"/>
+      <c r="M64" s="1050"/>
     </row>
     <row r="65" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E65" s="1050" t="s">
+      <c r="E65" s="1060" t="s">
         <v>96</v>
       </c>
       <c r="F65" s="61"/>
@@ -23138,7 +23140,7 @@
       <c r="M65" s="955"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E66" s="1051"/>
+      <c r="E66" s="1061"/>
       <c r="F66" s="64"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66" t="s">
@@ -23155,7 +23157,7 @@
       <c r="M66" s="955"/>
     </row>
     <row r="67" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E67" s="1051"/>
+      <c r="E67" s="1061"/>
       <c r="F67" s="64"/>
       <c r="G67" s="65"/>
       <c r="H67" s="66" t="s">
@@ -23172,7 +23174,7 @@
       <c r="M67" s="955"/>
     </row>
     <row r="68" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E68" s="1052"/>
+      <c r="E68" s="1073"/>
       <c r="F68" s="469" t="s">
         <v>25</v>
       </c>
@@ -23195,16 +23197,6 @@
     <row r="69" spans="5:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="M37:M64"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="L21:L26"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="L5:L20"/>
-    <mergeCell ref="L29:L36"/>
-    <mergeCell ref="L37:L64"/>
     <mergeCell ref="F3:K3"/>
     <mergeCell ref="J50:J52"/>
     <mergeCell ref="E65:E68"/>
@@ -23221,6 +23213,16 @@
     <mergeCell ref="E9:E12"/>
     <mergeCell ref="E13:E16"/>
     <mergeCell ref="E17:E20"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="L5:L20"/>
+    <mergeCell ref="L29:L36"/>
+    <mergeCell ref="L37:L64"/>
+    <mergeCell ref="M37:M64"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="L21:L26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23242,13 +23244,13 @@
       <c r="C4" s="466" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="1048" t="s">
+      <c r="D4" s="1071" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="1049"/>
-      <c r="F4" s="1049"/>
-      <c r="G4" s="1049"/>
-      <c r="H4" s="1049"/>
+      <c r="E4" s="1072"/>
+      <c r="F4" s="1072"/>
+      <c r="G4" s="1072"/>
+      <c r="H4" s="1072"/>
       <c r="I4" s="482"/>
     </row>
     <row r="5" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -23275,7 +23277,7 @@
       </c>
     </row>
     <row r="6" spans="3:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="1076" t="s">
+      <c r="C6" s="1085" t="s">
         <v>111</v>
       </c>
       <c r="D6" s="473"/>
@@ -23287,12 +23289,12 @@
       <c r="H6" s="480" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="1080" t="s">
+      <c r="I6" s="1076" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="1051"/>
+      <c r="C7" s="1061"/>
       <c r="D7" s="434"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
@@ -23300,10 +23302,10 @@
       <c r="H7" s="447" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="1081"/>
+      <c r="I7" s="1077"/>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="1051"/>
+      <c r="C8" s="1061"/>
       <c r="D8" s="434"/>
       <c r="E8" s="65"/>
       <c r="F8" s="65"/>
@@ -23311,10 +23313,10 @@
       <c r="H8" s="447" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="1081"/>
+      <c r="I8" s="1077"/>
     </row>
     <row r="9" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="1053"/>
+      <c r="C9" s="1062"/>
       <c r="D9" s="435" t="s">
         <v>73</v>
       </c>
@@ -23328,10 +23330,10 @@
       <c r="H9" s="468" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="1084"/>
+      <c r="I9" s="1078"/>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="1050" t="s">
+      <c r="C10" s="1060" t="s">
         <v>110</v>
       </c>
       <c r="D10" s="478"/>
@@ -23343,12 +23345,12 @@
       <c r="H10" s="493" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="1078" t="s">
+      <c r="I10" s="1079" t="s">
         <v>798</v>
       </c>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="1051"/>
+      <c r="C11" s="1061"/>
       <c r="D11" s="72"/>
       <c r="E11" s="73"/>
       <c r="F11" s="65"/>
@@ -23356,10 +23358,10 @@
       <c r="H11" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="1078"/>
+      <c r="I11" s="1079"/>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="1051"/>
+      <c r="C12" s="1061"/>
       <c r="D12" s="72"/>
       <c r="E12" s="73"/>
       <c r="F12" s="65"/>
@@ -23367,10 +23369,10 @@
       <c r="H12" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="1078"/>
+      <c r="I12" s="1079"/>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C13" s="1053"/>
+      <c r="C13" s="1062"/>
       <c r="D13" s="96"/>
       <c r="E13" s="97"/>
       <c r="F13" s="82" t="s">
@@ -23380,10 +23382,10 @@
       <c r="H13" s="491" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="1078"/>
+      <c r="I13" s="1079"/>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="1050" t="s">
+      <c r="C14" s="1060" t="s">
         <v>109</v>
       </c>
       <c r="D14" s="101"/>
@@ -23395,10 +23397,10 @@
       <c r="H14" s="495" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="1078"/>
+      <c r="I14" s="1079"/>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="1051"/>
+      <c r="C15" s="1061"/>
       <c r="D15" s="72"/>
       <c r="E15" s="73"/>
       <c r="F15" s="65"/>
@@ -23406,10 +23408,10 @@
       <c r="H15" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="1078"/>
+      <c r="I15" s="1079"/>
     </row>
     <row r="16" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="1051"/>
+      <c r="C16" s="1061"/>
       <c r="D16" s="96"/>
       <c r="E16" s="97"/>
       <c r="F16" s="65"/>
@@ -23417,10 +23419,10 @@
       <c r="H16" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="1078"/>
+      <c r="I16" s="1079"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C17" s="1053"/>
+      <c r="C17" s="1062"/>
       <c r="D17" s="104"/>
       <c r="E17" s="105"/>
       <c r="F17" s="113" t="s">
@@ -23430,10 +23432,10 @@
       <c r="H17" s="491" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="1078"/>
+      <c r="I17" s="1079"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C18" s="1050" t="s">
+      <c r="C18" s="1060" t="s">
         <v>108</v>
       </c>
       <c r="D18" s="98"/>
@@ -23445,10 +23447,10 @@
       <c r="H18" s="495" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="1078"/>
+      <c r="I18" s="1079"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C19" s="1051"/>
+      <c r="C19" s="1061"/>
       <c r="D19" s="72"/>
       <c r="E19" s="73"/>
       <c r="F19" s="65"/>
@@ -23456,10 +23458,10 @@
       <c r="H19" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="1078"/>
+      <c r="I19" s="1079"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="1051"/>
+      <c r="C20" s="1061"/>
       <c r="D20" s="96"/>
       <c r="E20" s="97"/>
       <c r="F20" s="65"/>
@@ -23467,10 +23469,10 @@
       <c r="H20" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="1078"/>
+      <c r="I20" s="1079"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="1053"/>
+      <c r="C21" s="1062"/>
       <c r="D21" s="104"/>
       <c r="E21" s="105"/>
       <c r="F21" s="82" t="s">
@@ -23480,10 +23482,10 @@
       <c r="H21" s="496" t="s">
         <v>32</v>
       </c>
-      <c r="I21" s="1078"/>
+      <c r="I21" s="1079"/>
     </row>
     <row r="22" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C22" s="1050" t="s">
+      <c r="C22" s="1060" t="s">
         <v>107</v>
       </c>
       <c r="D22" s="98"/>
@@ -23495,10 +23497,10 @@
       <c r="H22" s="494" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="1078"/>
+      <c r="I22" s="1079"/>
     </row>
     <row r="23" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C23" s="1051"/>
+      <c r="C23" s="1061"/>
       <c r="D23" s="72"/>
       <c r="E23" s="73"/>
       <c r="F23" s="65"/>
@@ -23506,10 +23508,10 @@
       <c r="H23" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="1078"/>
+      <c r="I23" s="1079"/>
     </row>
     <row r="24" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C24" s="1051"/>
+      <c r="C24" s="1061"/>
       <c r="D24" s="72"/>
       <c r="E24" s="73"/>
       <c r="F24" s="81"/>
@@ -23517,10 +23519,10 @@
       <c r="H24" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="1078"/>
+      <c r="I24" s="1079"/>
     </row>
     <row r="25" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="1053"/>
+      <c r="C25" s="1062"/>
       <c r="D25" s="96" t="s">
         <v>64</v>
       </c>
@@ -23534,10 +23536,10 @@
       <c r="H25" s="491" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="1079"/>
+      <c r="I25" s="1080"/>
     </row>
     <row r="26" spans="3:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="1050" t="s">
+      <c r="C26" s="1060" t="s">
         <v>106</v>
       </c>
       <c r="D26" s="474" t="s">
@@ -23560,7 +23562,7 @@
       </c>
     </row>
     <row r="27" spans="3:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="1051"/>
+      <c r="C27" s="1061"/>
       <c r="D27" s="438"/>
       <c r="E27" s="273"/>
       <c r="F27" s="62"/>
@@ -23570,12 +23572,12 @@
       <c r="H27" s="467" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="1085" t="s">
+      <c r="I27" s="1081" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="28" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="1051"/>
+      <c r="C28" s="1061"/>
       <c r="D28" s="436"/>
       <c r="E28" s="437"/>
       <c r="F28" s="81"/>
@@ -23583,10 +23585,10 @@
       <c r="H28" s="447" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="1081"/>
+      <c r="I28" s="1077"/>
     </row>
     <row r="29" spans="3:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="1053"/>
+      <c r="C29" s="1062"/>
       <c r="D29" s="436"/>
       <c r="E29" s="437"/>
       <c r="F29" s="82" t="s">
@@ -23617,7 +23619,7 @@
       </c>
     </row>
     <row r="30" spans="3:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="1050" t="s">
+      <c r="C30" s="1060" t="s">
         <v>105</v>
       </c>
       <c r="D30" s="439"/>
@@ -23640,12 +23642,12 @@
       <c r="N30" s="452" t="s">
         <v>32</v>
       </c>
-      <c r="O30" s="1080" t="s">
+      <c r="O30" s="1076" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="31" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C31" s="1051"/>
+      <c r="C31" s="1061"/>
       <c r="D31" s="64"/>
       <c r="E31" s="65"/>
       <c r="F31" s="65"/>
@@ -23664,10 +23666,10 @@
       <c r="N31" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="O31" s="1081"/>
+      <c r="O31" s="1077"/>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C32" s="1051"/>
+      <c r="C32" s="1061"/>
       <c r="D32" s="64"/>
       <c r="E32" s="65"/>
       <c r="F32" s="65"/>
@@ -23686,10 +23688,10 @@
       <c r="N32" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="O32" s="1081"/>
+      <c r="O32" s="1077"/>
     </row>
     <row r="33" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="1053"/>
+      <c r="C33" s="1062"/>
       <c r="D33" s="442" t="s">
         <v>73</v>
       </c>
@@ -23714,10 +23716,10 @@
       <c r="N33" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="O33" s="1081"/>
+      <c r="O33" s="1077"/>
     </row>
     <row r="34" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C34" s="1050" t="s">
+      <c r="C34" s="1060" t="s">
         <v>104</v>
       </c>
       <c r="D34" s="61"/>
@@ -23740,10 +23742,10 @@
       <c r="N34" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="O34" s="1081"/>
+      <c r="O34" s="1077"/>
     </row>
     <row r="35" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C35" s="1051"/>
+      <c r="C35" s="1061"/>
       <c r="D35" s="64"/>
       <c r="E35" s="65"/>
       <c r="F35" s="65"/>
@@ -23762,10 +23764,10 @@
       <c r="N35" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="O35" s="1081"/>
+      <c r="O35" s="1077"/>
     </row>
     <row r="36" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C36" s="1051"/>
+      <c r="C36" s="1061"/>
       <c r="D36" s="64"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65"/>
@@ -23784,10 +23786,10 @@
       <c r="N36" s="447" t="s">
         <v>33</v>
       </c>
-      <c r="O36" s="1081"/>
+      <c r="O36" s="1077"/>
     </row>
     <row r="37" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="1053"/>
+      <c r="C37" s="1062"/>
       <c r="D37" s="80" t="s">
         <v>73</v>
       </c>
@@ -23819,7 +23821,7 @@
       <c r="O37" s="1082"/>
     </row>
     <row r="38" spans="3:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="1050" t="s">
+      <c r="C38" s="1060" t="s">
         <v>103</v>
       </c>
       <c r="D38" s="439"/>
@@ -23835,7 +23837,7 @@
       </c>
     </row>
     <row r="39" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C39" s="1051"/>
+      <c r="C39" s="1061"/>
       <c r="D39" s="64"/>
       <c r="E39" s="65"/>
       <c r="F39" s="66" t="s">
@@ -23849,7 +23851,7 @@
       </c>
     </row>
     <row r="40" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C40" s="1051"/>
+      <c r="C40" s="1061"/>
       <c r="D40" s="64"/>
       <c r="E40" s="65"/>
       <c r="F40" s="66" t="s">
@@ -23863,7 +23865,7 @@
       </c>
     </row>
     <row r="41" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C41" s="1053"/>
+      <c r="C41" s="1062"/>
       <c r="D41" s="108"/>
       <c r="E41" s="109"/>
       <c r="F41" s="82" t="s">
@@ -23877,7 +23879,7 @@
       </c>
     </row>
     <row r="42" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C42" s="1050" t="s">
+      <c r="C42" s="1060" t="s">
         <v>102</v>
       </c>
       <c r="D42" s="61"/>
@@ -23893,7 +23895,7 @@
       </c>
     </row>
     <row r="43" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C43" s="1051"/>
+      <c r="C43" s="1061"/>
       <c r="D43" s="64"/>
       <c r="E43" s="65"/>
       <c r="F43" s="66" t="s">
@@ -23907,7 +23909,7 @@
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C44" s="1051"/>
+      <c r="C44" s="1061"/>
       <c r="D44" s="64"/>
       <c r="E44" s="65"/>
       <c r="F44" s="82" t="s">
@@ -23921,7 +23923,7 @@
       </c>
     </row>
     <row r="45" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C45" s="1053"/>
+      <c r="C45" s="1062"/>
       <c r="D45" s="80"/>
       <c r="E45" s="81"/>
       <c r="F45" s="113" t="s">
@@ -23935,7 +23937,7 @@
       </c>
     </row>
     <row r="46" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C46" s="1050" t="s">
+      <c r="C46" s="1060" t="s">
         <v>101</v>
       </c>
       <c r="D46" s="106"/>
@@ -23951,7 +23953,7 @@
       </c>
     </row>
     <row r="47" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C47" s="1054"/>
+      <c r="C47" s="1074"/>
       <c r="D47" s="64"/>
       <c r="E47" s="65"/>
       <c r="F47" s="66" t="s">
@@ -23965,7 +23967,7 @@
       </c>
     </row>
     <row r="48" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C48" s="1054"/>
+      <c r="C48" s="1074"/>
       <c r="D48" s="64"/>
       <c r="E48" s="65"/>
       <c r="F48" s="82" t="s">
@@ -23979,7 +23981,7 @@
       </c>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C49" s="1055"/>
+      <c r="C49" s="1075"/>
       <c r="D49" s="108"/>
       <c r="E49" s="109"/>
       <c r="F49" s="113" t="s">
@@ -23993,7 +23995,7 @@
       </c>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C50" s="1050" t="s">
+      <c r="C50" s="1060" t="s">
         <v>100</v>
       </c>
       <c r="D50" s="61"/>
@@ -24009,7 +24011,7 @@
       </c>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C51" s="1051"/>
+      <c r="C51" s="1061"/>
       <c r="D51" s="64"/>
       <c r="E51" s="65"/>
       <c r="F51" s="66" t="s">
@@ -24023,7 +24025,7 @@
       </c>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C52" s="1051"/>
+      <c r="C52" s="1061"/>
       <c r="D52" s="64"/>
       <c r="E52" s="65"/>
       <c r="F52" s="66" t="s">
@@ -24037,7 +24039,7 @@
       </c>
     </row>
     <row r="53" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="1053"/>
+      <c r="C53" s="1062"/>
       <c r="D53" s="442" t="s">
         <v>73</v>
       </c>
@@ -24055,7 +24057,7 @@
       </c>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C54" s="1050" t="s">
+      <c r="C54" s="1060" t="s">
         <v>99</v>
       </c>
       <c r="D54" s="61"/>
@@ -24071,7 +24073,7 @@
       </c>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C55" s="1051"/>
+      <c r="C55" s="1061"/>
       <c r="D55" s="64"/>
       <c r="E55" s="65"/>
       <c r="F55" s="66" t="s">
@@ -24085,7 +24087,7 @@
       </c>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C56" s="1051"/>
+      <c r="C56" s="1061"/>
       <c r="D56" s="80"/>
       <c r="E56" s="81"/>
       <c r="F56" s="66" t="s">
@@ -24099,7 +24101,7 @@
       </c>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C57" s="1053"/>
+      <c r="C57" s="1062"/>
       <c r="D57" s="108"/>
       <c r="E57" s="109"/>
       <c r="F57" s="82" t="s">
@@ -24113,7 +24115,7 @@
       </c>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="1050" t="s">
+      <c r="C58" s="1060" t="s">
         <v>98</v>
       </c>
       <c r="D58" s="61"/>
@@ -24129,7 +24131,7 @@
       </c>
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="1051"/>
+      <c r="C59" s="1061"/>
       <c r="D59" s="64"/>
       <c r="E59" s="65"/>
       <c r="F59" s="66" t="s">
@@ -24143,7 +24145,7 @@
       </c>
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C60" s="1051"/>
+      <c r="C60" s="1061"/>
       <c r="D60" s="80"/>
       <c r="E60" s="81"/>
       <c r="F60" s="66" t="s">
@@ -24157,7 +24159,7 @@
       </c>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C61" s="1053"/>
+      <c r="C61" s="1062"/>
       <c r="D61" s="80"/>
       <c r="E61" s="81"/>
       <c r="F61" s="82" t="s">
@@ -24171,7 +24173,7 @@
       </c>
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C62" s="1050" t="s">
+      <c r="C62" s="1060" t="s">
         <v>97</v>
       </c>
       <c r="D62" s="106"/>
@@ -24187,7 +24189,7 @@
       </c>
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C63" s="1051"/>
+      <c r="C63" s="1061"/>
       <c r="D63" s="64"/>
       <c r="E63" s="65"/>
       <c r="F63" s="66" t="s">
@@ -24201,7 +24203,7 @@
       </c>
     </row>
     <row r="64" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="1051"/>
+      <c r="C64" s="1061"/>
       <c r="D64" s="64"/>
       <c r="E64" s="65"/>
       <c r="F64" s="66" t="s">
@@ -24215,7 +24217,7 @@
       </c>
     </row>
     <row r="65" spans="3:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="1053"/>
+      <c r="C65" s="1062"/>
       <c r="D65" s="110"/>
       <c r="E65" s="109"/>
       <c r="F65" s="113" t="s">
@@ -24247,7 +24249,7 @@
       </c>
     </row>
     <row r="66" spans="3:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="1050" t="s">
+      <c r="C66" s="1060" t="s">
         <v>96</v>
       </c>
       <c r="D66" s="61"/>
@@ -24261,7 +24263,7 @@
       <c r="H66" s="467" t="s">
         <v>33</v>
       </c>
-      <c r="I66" s="1083"/>
+      <c r="I66" s="1084"/>
       <c r="J66" s="463"/>
       <c r="K66" s="464"/>
       <c r="L66" s="453" t="s">
@@ -24273,12 +24275,12 @@
       <c r="N66" s="465" t="s">
         <v>33</v>
       </c>
-      <c r="O66" s="1077" t="s">
+      <c r="O66" s="1083" t="s">
         <v>793</v>
       </c>
     </row>
     <row r="67" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C67" s="1051"/>
+      <c r="C67" s="1061"/>
       <c r="D67" s="64"/>
       <c r="E67" s="65"/>
       <c r="F67" s="66" t="s">
@@ -24290,7 +24292,7 @@
       <c r="H67" s="447" t="s">
         <v>33</v>
       </c>
-      <c r="I67" s="1083"/>
+      <c r="I67" s="1084"/>
       <c r="J67" s="455"/>
       <c r="K67" s="65"/>
       <c r="L67" s="66" t="s">
@@ -24302,10 +24304,10 @@
       <c r="N67" s="461" t="s">
         <v>32</v>
       </c>
-      <c r="O67" s="1078"/>
+      <c r="O67" s="1079"/>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C68" s="1051"/>
+      <c r="C68" s="1061"/>
       <c r="D68" s="64"/>
       <c r="E68" s="65"/>
       <c r="F68" s="66" t="s">
@@ -24317,7 +24319,7 @@
       <c r="H68" s="447" t="s">
         <v>33</v>
       </c>
-      <c r="I68" s="1083"/>
+      <c r="I68" s="1084"/>
       <c r="J68" s="455"/>
       <c r="K68" s="65"/>
       <c r="L68" s="66" t="s">
@@ -24329,10 +24331,10 @@
       <c r="N68" s="461" t="s">
         <v>32</v>
       </c>
-      <c r="O68" s="1078"/>
+      <c r="O68" s="1079"/>
     </row>
     <row r="69" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="1052"/>
+      <c r="C69" s="1073"/>
       <c r="D69" s="469" t="s">
         <v>73</v>
       </c>
@@ -24348,7 +24350,7 @@
       <c r="H69" s="448" t="s">
         <v>33</v>
       </c>
-      <c r="I69" s="1083"/>
+      <c r="I69" s="1084"/>
       <c r="J69" s="456" t="s">
         <v>25</v>
       </c>
@@ -24364,16 +24366,16 @@
       <c r="N69" s="462" t="s">
         <v>32</v>
       </c>
-      <c r="O69" s="1079"/>
+      <c r="O69" s="1080"/>
     </row>
     <row r="70" spans="3:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="I6:I9"/>
-    <mergeCell ref="I10:I25"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C18:C21"/>
     <mergeCell ref="O66:O69"/>
     <mergeCell ref="O30:O37"/>
     <mergeCell ref="C38:C41"/>
@@ -24387,11 +24389,11 @@
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="C66:C69"/>
     <mergeCell ref="I66:I69"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="I6:I9"/>
+    <mergeCell ref="I10:I25"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="I27:I29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
